--- a/src/hydrofia/hydrofia_ph_template - kopia.xlsx
+++ b/src/hydrofia/hydrofia_ph_template - kopia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mw\git\hydrofia\hydrofia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hydrofia\src\hydrofia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AFFFE7-6472-45BB-9DC1-95DF68E2B603}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA8DF2F-E4EE-4081-B15C-057EF51A0181}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="165" windowWidth="15600" windowHeight="11610" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="170" windowWidth="15600" windowHeight="11610" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rådata" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Verifiering" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">OFFSET('Rapport för utskrift'!$A$1,0,0,12+COUNTA(#REF!),12)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">OFFSET('Rapport för utskrift'!#REF!,0,0,12+COUNTA(#REF!),12)</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Rapport för utskrift'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
     <author>Nilsson Madeleine</author>
   </authors>
   <commentList>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{54CF2BBA-37EA-458E-AE20-E6019E698CD6}">
       <text>
         <r>
           <rPr>
@@ -47,7 +47,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="1" shapeId="0" xr:uid="{21853188-1459-4735-90C6-F9F3174E1258}">
+    <comment ref="J10" authorId="1" shapeId="0" xr:uid="{ED46D35A-ECD8-4CF7-8B98-A5606CBF59F6}">
       <text>
         <r>
           <rPr>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="833">
   <si>
     <t>Djup</t>
   </si>
@@ -1348,15 +1348,6 @@
     <t>Skapat verifieringsdata-flik</t>
   </si>
   <si>
-    <t>Sign</t>
-  </si>
-  <si>
-    <t>ml</t>
-  </si>
-  <si>
-    <t>ml/l</t>
-  </si>
-  <si>
     <t>Lagt till kolumn för Sign</t>
   </si>
   <si>
@@ -2590,16 +2581,22 @@
     <t>Temp</t>
   </si>
   <si>
-    <t>pH</t>
-  </si>
-  <si>
     <t>Djup (ref)</t>
   </si>
   <si>
-    <t>pH (in-situ)</t>
-  </si>
-  <si>
     <t>Datum</t>
+  </si>
+  <si>
+    <t>Lab. Temp</t>
+  </si>
+  <si>
+    <t>pH-TOT-labT</t>
+  </si>
+  <si>
+    <t>pH-TOT-25</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
@@ -2611,7 +2608,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="[$-41D]General"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2667,13 +2664,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="30"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2779,7 +2769,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2826,13 +2816,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color theme="1"/>
+      </right>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2852,13 +2890,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2867,23 +2905,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2903,23 +2932,37 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2927,36 +2970,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2968,23 +2991,35 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2992,15 +3027,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 4" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3018,22 +3045,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>260874</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>169500</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>156099</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>125050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="\\winfs-proj\data\proj\havgem\MOL\Labinfo\SMHI-logga.png">
+        <xdr:cNvPr id="4" name="Picture 1" descr="\\winfs-proj\data\proj\havgem\MOL\Labinfo\SMHI-logga.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DD54A84-A1A6-43DF-9DAB-D32309D8A6F7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3056,8 +3083,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="879999" cy="360000"/>
+          <a:off x="28575" y="142875"/>
+          <a:ext cx="876824" cy="363175"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3401,7 +3428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8B184CC-18AA-4DD3-91F3-47A3A5EC6B5D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3412,2589 +3439,2101 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:EK112"/>
-  <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:DV111"/>
+  <sheetFormatPr defaultColWidth="28.7265625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="4.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="11" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="11" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" style="11" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="10" style="11" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" style="11" customWidth="1"/>
-    <col min="13" max="13" width="17.28515625" style="11" customWidth="1"/>
-    <col min="14" max="22" width="10.7109375" style="11" customWidth="1"/>
-    <col min="23" max="16384" width="28.7109375" style="11"/>
+    <col min="1" max="1" width="15.7265625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" style="11" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" style="11" customWidth="1"/>
+    <col min="5" max="6" width="7.81640625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" style="11" customWidth="1"/>
+    <col min="8" max="9" width="13.26953125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" style="11" customWidth="1"/>
+    <col min="11" max="16384" width="28.7265625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:141" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:126" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="41" t="s">
-        <v>827</v>
-      </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="K1" s="36" t="s">
-        <v>833</v>
-      </c>
+      <c r="B1" s="36" t="s">
+        <v>824</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="H1" s="41" t="s">
+        <v>828</v>
+      </c>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
       <c r="M1" s="12"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
-      <c r="AJ1" s="13"/>
-      <c r="AK1" s="13"/>
-      <c r="AL1" s="13"/>
-      <c r="AM1" s="13"/>
-      <c r="AN1" s="13"/>
-      <c r="AO1" s="13"/>
-      <c r="AP1" s="13"/>
-      <c r="AQ1" s="13"/>
-      <c r="AR1" s="13"/>
-      <c r="AS1" s="13"/>
-      <c r="AT1" s="13"/>
-      <c r="AU1" s="13"/>
-      <c r="AV1" s="13"/>
-      <c r="AW1" s="13"/>
-      <c r="AX1" s="13"/>
-      <c r="AY1" s="13"/>
-      <c r="AZ1" s="13"/>
-      <c r="BA1" s="13"/>
-      <c r="BB1" s="13"/>
-      <c r="BC1" s="13"/>
-      <c r="BD1" s="13"/>
-      <c r="BE1" s="13"/>
-      <c r="BF1" s="13"/>
-      <c r="BG1" s="13"/>
-      <c r="BH1" s="13"/>
-      <c r="BI1" s="13"/>
-      <c r="BJ1" s="13"/>
-      <c r="BK1" s="13"/>
-      <c r="BL1" s="13"/>
-      <c r="BM1" s="13"/>
-      <c r="BN1" s="13"/>
-      <c r="BO1" s="13"/>
-      <c r="BP1" s="13"/>
-      <c r="BQ1" s="13"/>
-      <c r="BR1" s="13"/>
-      <c r="BS1" s="13"/>
-      <c r="BT1" s="13"/>
-      <c r="BU1" s="13"/>
-      <c r="BV1" s="13"/>
-      <c r="BW1" s="13"/>
-      <c r="BX1" s="13"/>
-      <c r="BY1" s="13"/>
-      <c r="BZ1" s="13"/>
-      <c r="CA1" s="13"/>
-      <c r="CB1" s="13"/>
-      <c r="CC1" s="13"/>
-      <c r="CD1" s="13"/>
-      <c r="CE1" s="13"/>
-      <c r="CF1" s="13"/>
-      <c r="CG1" s="13"/>
-      <c r="CH1" s="13"/>
-      <c r="CI1" s="13"/>
-      <c r="CJ1" s="13"/>
-      <c r="CK1" s="13"/>
-      <c r="CL1" s="13"/>
-      <c r="CM1" s="13"/>
-      <c r="CN1" s="13"/>
-      <c r="CO1" s="13"/>
-      <c r="CP1" s="13"/>
-      <c r="CQ1" s="13"/>
-      <c r="CR1" s="13"/>
-      <c r="CS1" s="13"/>
-      <c r="CT1" s="13"/>
-      <c r="CU1" s="13"/>
-      <c r="CV1" s="13"/>
-      <c r="CW1" s="13"/>
-      <c r="CX1" s="13"/>
-      <c r="CY1" s="13"/>
-      <c r="CZ1" s="13"/>
-      <c r="DA1" s="13"/>
-      <c r="DB1" s="13"/>
-      <c r="DC1" s="13"/>
-      <c r="DD1" s="13"/>
-      <c r="DE1" s="13"/>
-      <c r="DF1" s="13"/>
-      <c r="DG1" s="13"/>
-      <c r="DH1" s="13"/>
-      <c r="DI1" s="13"/>
-      <c r="DJ1" s="13"/>
-      <c r="DK1" s="13"/>
-      <c r="DL1" s="13"/>
-      <c r="DM1" s="13"/>
-      <c r="DN1" s="13"/>
-      <c r="DO1" s="13"/>
-      <c r="DP1" s="13"/>
-      <c r="DQ1" s="13"/>
-      <c r="DR1" s="13"/>
-      <c r="DS1" s="13"/>
-      <c r="DT1" s="13"/>
-      <c r="DU1" s="13"/>
-      <c r="DV1" s="13"/>
-      <c r="DW1" s="13"/>
-      <c r="DX1" s="13"/>
-      <c r="DY1" s="13"/>
-      <c r="DZ1" s="13"/>
-      <c r="EA1" s="13"/>
-      <c r="EB1" s="13"/>
-      <c r="EC1" s="13"/>
-      <c r="ED1" s="13"/>
-      <c r="EE1" s="13"/>
-      <c r="EF1" s="13"/>
-      <c r="EG1" s="13"/>
-      <c r="EH1" s="13"/>
-      <c r="EI1" s="13"/>
-      <c r="EJ1" s="13"/>
-      <c r="EK1" s="13"/>
-    </row>
-    <row r="2" spans="1:141" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="35"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="K2" s="36" t="s">
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="12"/>
+      <c r="AE1" s="12"/>
+      <c r="AF1" s="12"/>
+      <c r="AG1" s="12"/>
+      <c r="AH1" s="12"/>
+      <c r="AI1" s="12"/>
+      <c r="AJ1" s="12"/>
+      <c r="AK1" s="12"/>
+      <c r="AL1" s="12"/>
+      <c r="AM1" s="12"/>
+      <c r="AN1" s="12"/>
+      <c r="AO1" s="12"/>
+      <c r="AP1" s="12"/>
+      <c r="AQ1" s="12"/>
+      <c r="AR1" s="12"/>
+      <c r="AS1" s="12"/>
+      <c r="AT1" s="12"/>
+      <c r="AU1" s="12"/>
+      <c r="AV1" s="12"/>
+      <c r="AW1" s="12"/>
+      <c r="AX1" s="12"/>
+      <c r="AY1" s="12"/>
+      <c r="AZ1" s="12"/>
+      <c r="BA1" s="12"/>
+      <c r="BB1" s="12"/>
+      <c r="BC1" s="12"/>
+      <c r="BD1" s="12"/>
+      <c r="BE1" s="12"/>
+      <c r="BF1" s="12"/>
+      <c r="BG1" s="12"/>
+      <c r="BH1" s="12"/>
+      <c r="BI1" s="12"/>
+      <c r="BJ1" s="12"/>
+      <c r="BK1" s="12"/>
+      <c r="BL1" s="12"/>
+      <c r="BM1" s="12"/>
+      <c r="BN1" s="12"/>
+      <c r="BO1" s="12"/>
+      <c r="BP1" s="12"/>
+      <c r="BQ1" s="12"/>
+      <c r="BR1" s="12"/>
+      <c r="BS1" s="12"/>
+      <c r="BT1" s="12"/>
+      <c r="BU1" s="12"/>
+      <c r="BV1" s="12"/>
+      <c r="BW1" s="12"/>
+      <c r="BX1" s="12"/>
+      <c r="BY1" s="12"/>
+      <c r="BZ1" s="12"/>
+      <c r="CA1" s="12"/>
+      <c r="CB1" s="12"/>
+      <c r="CC1" s="12"/>
+      <c r="CD1" s="12"/>
+      <c r="CE1" s="12"/>
+      <c r="CF1" s="12"/>
+      <c r="CG1" s="12"/>
+      <c r="CH1" s="12"/>
+      <c r="CI1" s="12"/>
+      <c r="CJ1" s="12"/>
+      <c r="CK1" s="12"/>
+      <c r="CL1" s="12"/>
+      <c r="CM1" s="12"/>
+      <c r="CN1" s="12"/>
+      <c r="CO1" s="12"/>
+      <c r="CP1" s="12"/>
+      <c r="CQ1" s="12"/>
+      <c r="CR1" s="12"/>
+      <c r="CS1" s="12"/>
+      <c r="CT1" s="12"/>
+      <c r="CU1" s="12"/>
+      <c r="CV1" s="12"/>
+      <c r="CW1" s="12"/>
+      <c r="CX1" s="12"/>
+      <c r="CY1" s="12"/>
+      <c r="CZ1" s="12"/>
+      <c r="DA1" s="12"/>
+      <c r="DB1" s="12"/>
+      <c r="DC1" s="12"/>
+      <c r="DD1" s="12"/>
+      <c r="DE1" s="12"/>
+      <c r="DF1" s="12"/>
+      <c r="DG1" s="12"/>
+      <c r="DH1" s="12"/>
+      <c r="DI1" s="12"/>
+      <c r="DJ1" s="12"/>
+      <c r="DK1" s="12"/>
+      <c r="DL1" s="12"/>
+      <c r="DM1" s="12"/>
+      <c r="DN1" s="12"/>
+      <c r="DO1" s="12"/>
+      <c r="DP1" s="12"/>
+      <c r="DQ1" s="12"/>
+      <c r="DR1" s="12"/>
+      <c r="DS1" s="12"/>
+      <c r="DT1" s="12"/>
+      <c r="DU1" s="12"/>
+      <c r="DV1" s="12"/>
+    </row>
+    <row r="2" spans="1:126" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="H2" s="41" t="s">
         <v>2</v>
       </c>
+      <c r="I2" s="41"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
       <c r="M2" s="12"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="13"/>
-      <c r="AC2" s="13"/>
-      <c r="AD2" s="13"/>
-      <c r="AE2" s="13"/>
-      <c r="AF2" s="13"/>
-      <c r="AG2" s="13"/>
-      <c r="AH2" s="13"/>
-      <c r="AI2" s="13"/>
-      <c r="AJ2" s="13"/>
-      <c r="AK2" s="13"/>
-      <c r="AL2" s="13"/>
-      <c r="AM2" s="13"/>
-      <c r="AN2" s="13"/>
-      <c r="AO2" s="13"/>
-      <c r="AP2" s="13"/>
-      <c r="AQ2" s="13"/>
-      <c r="AR2" s="13"/>
-      <c r="AS2" s="13"/>
-      <c r="AT2" s="13"/>
-      <c r="AU2" s="13"/>
-      <c r="AV2" s="13"/>
-      <c r="AW2" s="13"/>
-      <c r="AX2" s="13"/>
-      <c r="AY2" s="13"/>
-      <c r="AZ2" s="13"/>
-      <c r="BA2" s="13"/>
-      <c r="BB2" s="13"/>
-      <c r="BC2" s="13"/>
-      <c r="BD2" s="13"/>
-      <c r="BE2" s="13"/>
-      <c r="BF2" s="13"/>
-      <c r="BG2" s="13"/>
-      <c r="BH2" s="13"/>
-      <c r="BI2" s="13"/>
-      <c r="BJ2" s="13"/>
-      <c r="BK2" s="13"/>
-      <c r="BL2" s="13"/>
-      <c r="BM2" s="13"/>
-      <c r="BN2" s="13"/>
-      <c r="BO2" s="13"/>
-      <c r="BP2" s="13"/>
-      <c r="BQ2" s="13"/>
-      <c r="BR2" s="13"/>
-      <c r="BS2" s="13"/>
-      <c r="BT2" s="13"/>
-      <c r="BU2" s="13"/>
-      <c r="BV2" s="13"/>
-      <c r="BW2" s="13"/>
-      <c r="BX2" s="13"/>
-      <c r="BY2" s="13"/>
-      <c r="BZ2" s="13"/>
-      <c r="CA2" s="13"/>
-      <c r="CB2" s="13"/>
-      <c r="CC2" s="13"/>
-      <c r="CD2" s="13"/>
-      <c r="CE2" s="13"/>
-      <c r="CF2" s="13"/>
-      <c r="CG2" s="13"/>
-      <c r="CH2" s="13"/>
-      <c r="CI2" s="13"/>
-      <c r="CJ2" s="13"/>
-      <c r="CK2" s="13"/>
-      <c r="CL2" s="13"/>
-      <c r="CM2" s="13"/>
-      <c r="CN2" s="13"/>
-      <c r="CO2" s="13"/>
-      <c r="CP2" s="13"/>
-      <c r="CQ2" s="13"/>
-      <c r="CR2" s="13"/>
-      <c r="CS2" s="13"/>
-      <c r="CT2" s="13"/>
-      <c r="CU2" s="13"/>
-      <c r="CV2" s="13"/>
-      <c r="CW2" s="13"/>
-      <c r="CX2" s="13"/>
-      <c r="CY2" s="13"/>
-      <c r="CZ2" s="13"/>
-      <c r="DA2" s="13"/>
-      <c r="DB2" s="13"/>
-      <c r="DC2" s="13"/>
-      <c r="DD2" s="13"/>
-      <c r="DE2" s="13"/>
-      <c r="DF2" s="13"/>
-      <c r="DG2" s="13"/>
-      <c r="DH2" s="13"/>
-      <c r="DI2" s="13"/>
-      <c r="DJ2" s="13"/>
-      <c r="DK2" s="13"/>
-      <c r="DL2" s="13"/>
-      <c r="DM2" s="13"/>
-      <c r="DN2" s="13"/>
-      <c r="DO2" s="13"/>
-      <c r="DP2" s="13"/>
-      <c r="DQ2" s="13"/>
-      <c r="DR2" s="13"/>
-      <c r="DS2" s="13"/>
-      <c r="DT2" s="13"/>
-      <c r="DU2" s="13"/>
-      <c r="DV2" s="13"/>
-      <c r="DW2" s="13"/>
-      <c r="DX2" s="13"/>
-      <c r="DY2" s="13"/>
-      <c r="DZ2" s="13"/>
-      <c r="EA2" s="13"/>
-      <c r="EB2" s="13"/>
-      <c r="EC2" s="13"/>
-      <c r="ED2" s="13"/>
-      <c r="EE2" s="13"/>
-      <c r="EF2" s="13"/>
-      <c r="EG2" s="13"/>
-      <c r="EH2" s="13"/>
-      <c r="EI2" s="13"/>
-      <c r="EJ2" s="13"/>
-      <c r="EK2" s="13"/>
-    </row>
-    <row r="3" spans="1:141" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
+      <c r="AH2" s="12"/>
+      <c r="AI2" s="12"/>
+      <c r="AJ2" s="12"/>
+      <c r="AK2" s="12"/>
+      <c r="AL2" s="12"/>
+      <c r="AM2" s="12"/>
+      <c r="AN2" s="12"/>
+      <c r="AO2" s="12"/>
+      <c r="AP2" s="12"/>
+      <c r="AQ2" s="12"/>
+      <c r="AR2" s="12"/>
+      <c r="AS2" s="12"/>
+      <c r="AT2" s="12"/>
+      <c r="AU2" s="12"/>
+      <c r="AV2" s="12"/>
+      <c r="AW2" s="12"/>
+      <c r="AX2" s="12"/>
+      <c r="AY2" s="12"/>
+      <c r="AZ2" s="12"/>
+      <c r="BA2" s="12"/>
+      <c r="BB2" s="12"/>
+      <c r="BC2" s="12"/>
+      <c r="BD2" s="12"/>
+      <c r="BE2" s="12"/>
+      <c r="BF2" s="12"/>
+      <c r="BG2" s="12"/>
+      <c r="BH2" s="12"/>
+      <c r="BI2" s="12"/>
+      <c r="BJ2" s="12"/>
+      <c r="BK2" s="12"/>
+      <c r="BL2" s="12"/>
+      <c r="BM2" s="12"/>
+      <c r="BN2" s="12"/>
+      <c r="BO2" s="12"/>
+      <c r="BP2" s="12"/>
+      <c r="BQ2" s="12"/>
+      <c r="BR2" s="12"/>
+      <c r="BS2" s="12"/>
+      <c r="BT2" s="12"/>
+      <c r="BU2" s="12"/>
+      <c r="BV2" s="12"/>
+      <c r="BW2" s="12"/>
+      <c r="BX2" s="12"/>
+      <c r="BY2" s="12"/>
+      <c r="BZ2" s="12"/>
+      <c r="CA2" s="12"/>
+      <c r="CB2" s="12"/>
+      <c r="CC2" s="12"/>
+      <c r="CD2" s="12"/>
+      <c r="CE2" s="12"/>
+      <c r="CF2" s="12"/>
+      <c r="CG2" s="12"/>
+      <c r="CH2" s="12"/>
+      <c r="CI2" s="12"/>
+      <c r="CJ2" s="12"/>
+      <c r="CK2" s="12"/>
+      <c r="CL2" s="12"/>
+      <c r="CM2" s="12"/>
+      <c r="CN2" s="12"/>
+      <c r="CO2" s="12"/>
+      <c r="CP2" s="12"/>
+      <c r="CQ2" s="12"/>
+      <c r="CR2" s="12"/>
+      <c r="CS2" s="12"/>
+      <c r="CT2" s="12"/>
+      <c r="CU2" s="12"/>
+      <c r="CV2" s="12"/>
+      <c r="CW2" s="12"/>
+      <c r="CX2" s="12"/>
+      <c r="CY2" s="12"/>
+      <c r="CZ2" s="12"/>
+      <c r="DA2" s="12"/>
+      <c r="DB2" s="12"/>
+      <c r="DC2" s="12"/>
+      <c r="DD2" s="12"/>
+      <c r="DE2" s="12"/>
+      <c r="DF2" s="12"/>
+      <c r="DG2" s="12"/>
+      <c r="DH2" s="12"/>
+      <c r="DI2" s="12"/>
+      <c r="DJ2" s="12"/>
+      <c r="DK2" s="12"/>
+      <c r="DL2" s="12"/>
+      <c r="DM2" s="12"/>
+      <c r="DN2" s="12"/>
+      <c r="DO2" s="12"/>
+      <c r="DP2" s="12"/>
+      <c r="DQ2" s="12"/>
+      <c r="DR2" s="12"/>
+      <c r="DS2" s="12"/>
+      <c r="DT2" s="12"/>
+      <c r="DU2" s="12"/>
+      <c r="DV2" s="12"/>
+    </row>
+    <row r="3" spans="1:126" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="12"/>
+      <c r="AA3" s="12"/>
+      <c r="AB3" s="12"/>
+      <c r="AC3" s="12"/>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="12"/>
+      <c r="AF3" s="12"/>
+      <c r="AG3" s="12"/>
+      <c r="AH3" s="12"/>
+      <c r="AI3" s="12"/>
+      <c r="AJ3" s="12"/>
+      <c r="AK3" s="12"/>
+      <c r="AL3" s="12"/>
+      <c r="AM3" s="12"/>
+      <c r="AN3" s="12"/>
+      <c r="AO3" s="12"/>
+      <c r="AP3" s="12"/>
+      <c r="AQ3" s="12"/>
+      <c r="AR3" s="12"/>
+      <c r="AS3" s="12"/>
+      <c r="AT3" s="12"/>
+      <c r="AU3" s="12"/>
+      <c r="AV3" s="12"/>
+      <c r="AW3" s="12"/>
+      <c r="AX3" s="12"/>
+      <c r="AY3" s="12"/>
+      <c r="AZ3" s="12"/>
+      <c r="BA3" s="12"/>
+      <c r="BB3" s="12"/>
+      <c r="BC3" s="12"/>
+      <c r="BD3" s="12"/>
+      <c r="BE3" s="12"/>
+      <c r="BF3" s="12"/>
+      <c r="BG3" s="12"/>
+      <c r="BH3" s="12"/>
+      <c r="BI3" s="12"/>
+      <c r="BJ3" s="12"/>
+      <c r="BK3" s="12"/>
+      <c r="BL3" s="12"/>
+      <c r="BM3" s="12"/>
+      <c r="BN3" s="12"/>
+      <c r="BO3" s="12"/>
+      <c r="BP3" s="12"/>
+      <c r="BQ3" s="12"/>
+      <c r="BR3" s="12"/>
+      <c r="BS3" s="12"/>
+      <c r="BT3" s="12"/>
+      <c r="BU3" s="12"/>
+      <c r="BV3" s="12"/>
+      <c r="BW3" s="12"/>
+      <c r="BX3" s="12"/>
+      <c r="BY3" s="12"/>
+      <c r="BZ3" s="12"/>
+      <c r="CA3" s="12"/>
+      <c r="CB3" s="12"/>
+      <c r="CC3" s="12"/>
+      <c r="CD3" s="12"/>
+      <c r="CE3" s="12"/>
+      <c r="CF3" s="12"/>
+      <c r="CG3" s="12"/>
+      <c r="CH3" s="12"/>
+      <c r="CI3" s="12"/>
+      <c r="CJ3" s="12"/>
+      <c r="CK3" s="12"/>
+      <c r="CL3" s="12"/>
+      <c r="CM3" s="12"/>
+      <c r="CN3" s="12"/>
+      <c r="CO3" s="12"/>
+      <c r="CP3" s="12"/>
+      <c r="CQ3" s="12"/>
+      <c r="CR3" s="12"/>
+      <c r="CS3" s="12"/>
+      <c r="CT3" s="12"/>
+      <c r="CU3" s="12"/>
+      <c r="CV3" s="12"/>
+      <c r="CW3" s="12"/>
+      <c r="CX3" s="12"/>
+      <c r="CY3" s="12"/>
+      <c r="CZ3" s="12"/>
+      <c r="DA3" s="12"/>
+      <c r="DB3" s="12"/>
+      <c r="DC3" s="12"/>
+      <c r="DD3" s="12"/>
+      <c r="DE3" s="12"/>
+      <c r="DF3" s="12"/>
+      <c r="DG3" s="12"/>
+      <c r="DH3" s="12"/>
+      <c r="DI3" s="12"/>
+      <c r="DJ3" s="12"/>
+      <c r="DK3" s="12"/>
+      <c r="DL3" s="12"/>
+      <c r="DM3" s="12"/>
+      <c r="DN3" s="12"/>
+      <c r="DO3" s="12"/>
+      <c r="DP3" s="12"/>
+      <c r="DQ3" s="12"/>
+      <c r="DR3" s="12"/>
+      <c r="DS3" s="12"/>
+      <c r="DT3" s="12"/>
+      <c r="DU3" s="12"/>
+      <c r="DV3" s="12"/>
+    </row>
+    <row r="4" spans="1:126" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="12"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
-      <c r="AE3" s="13"/>
-      <c r="AF3" s="13"/>
-      <c r="AG3" s="13"/>
-      <c r="AH3" s="13"/>
-      <c r="AI3" s="13"/>
-      <c r="AJ3" s="13"/>
-      <c r="AK3" s="13"/>
-      <c r="AL3" s="13"/>
-      <c r="AM3" s="13"/>
-      <c r="AN3" s="13"/>
-      <c r="AO3" s="13"/>
-      <c r="AP3" s="13"/>
-      <c r="AQ3" s="13"/>
-      <c r="AR3" s="13"/>
-      <c r="AS3" s="13"/>
-      <c r="AT3" s="13"/>
-      <c r="AU3" s="13"/>
-      <c r="AV3" s="13"/>
-      <c r="AW3" s="13"/>
-      <c r="AX3" s="13"/>
-      <c r="AY3" s="13"/>
-      <c r="AZ3" s="13"/>
-      <c r="BA3" s="13"/>
-      <c r="BB3" s="13"/>
-      <c r="BC3" s="13"/>
-      <c r="BD3" s="13"/>
-      <c r="BE3" s="13"/>
-      <c r="BF3" s="13"/>
-      <c r="BG3" s="13"/>
-      <c r="BH3" s="13"/>
-      <c r="BI3" s="13"/>
-      <c r="BJ3" s="13"/>
-      <c r="BK3" s="13"/>
-      <c r="BL3" s="13"/>
-      <c r="BM3" s="13"/>
-      <c r="BN3" s="13"/>
-      <c r="BO3" s="13"/>
-      <c r="BP3" s="13"/>
-      <c r="BQ3" s="13"/>
-      <c r="BR3" s="13"/>
-      <c r="BS3" s="13"/>
-      <c r="BT3" s="13"/>
-      <c r="BU3" s="13"/>
-      <c r="BV3" s="13"/>
-      <c r="BW3" s="13"/>
-      <c r="BX3" s="13"/>
-      <c r="BY3" s="13"/>
-      <c r="BZ3" s="13"/>
-      <c r="CA3" s="13"/>
-      <c r="CB3" s="13"/>
-      <c r="CC3" s="13"/>
-      <c r="CD3" s="13"/>
-      <c r="CE3" s="13"/>
-      <c r="CF3" s="13"/>
-      <c r="CG3" s="13"/>
-      <c r="CH3" s="13"/>
-      <c r="CI3" s="13"/>
-      <c r="CJ3" s="13"/>
-      <c r="CK3" s="13"/>
-      <c r="CL3" s="13"/>
-      <c r="CM3" s="13"/>
-      <c r="CN3" s="13"/>
-      <c r="CO3" s="13"/>
-      <c r="CP3" s="13"/>
-      <c r="CQ3" s="13"/>
-      <c r="CR3" s="13"/>
-      <c r="CS3" s="13"/>
-      <c r="CT3" s="13"/>
-      <c r="CU3" s="13"/>
-      <c r="CV3" s="13"/>
-      <c r="CW3" s="13"/>
-      <c r="CX3" s="13"/>
-      <c r="CY3" s="13"/>
-      <c r="CZ3" s="13"/>
-      <c r="DA3" s="13"/>
-      <c r="DB3" s="13"/>
-      <c r="DC3" s="13"/>
-      <c r="DD3" s="13"/>
-      <c r="DE3" s="13"/>
-      <c r="DF3" s="13"/>
-      <c r="DG3" s="13"/>
-      <c r="DH3" s="13"/>
-      <c r="DI3" s="13"/>
-      <c r="DJ3" s="13"/>
-      <c r="DK3" s="13"/>
-      <c r="DL3" s="13"/>
-      <c r="DM3" s="13"/>
-      <c r="DN3" s="13"/>
-      <c r="DO3" s="13"/>
-      <c r="DP3" s="13"/>
-      <c r="DQ3" s="13"/>
-      <c r="DR3" s="13"/>
-      <c r="DS3" s="13"/>
-      <c r="DT3" s="13"/>
-      <c r="DU3" s="13"/>
-      <c r="DV3" s="13"/>
-      <c r="DW3" s="13"/>
-      <c r="DX3" s="13"/>
-      <c r="DY3" s="13"/>
-      <c r="DZ3" s="13"/>
-      <c r="EA3" s="13"/>
-      <c r="EB3" s="13"/>
-      <c r="EC3" s="13"/>
-      <c r="ED3" s="13"/>
-      <c r="EE3" s="13"/>
-      <c r="EF3" s="13"/>
-      <c r="EG3" s="13"/>
-      <c r="EH3" s="13"/>
-      <c r="EI3" s="13"/>
-      <c r="EJ3" s="13"/>
-      <c r="EK3" s="13"/>
-    </row>
-    <row r="4" spans="1:141" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="35"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="13"/>
-      <c r="AF4" s="13"/>
-      <c r="AG4" s="13"/>
-      <c r="AH4" s="13"/>
-      <c r="AI4" s="13"/>
-      <c r="AJ4" s="13"/>
-      <c r="AK4" s="13"/>
-      <c r="AL4" s="13"/>
-      <c r="AM4" s="13"/>
-      <c r="AN4" s="13"/>
-      <c r="AO4" s="13"/>
-      <c r="AP4" s="13"/>
-      <c r="AQ4" s="13"/>
-      <c r="AR4" s="13"/>
-      <c r="AS4" s="13"/>
-      <c r="AT4" s="13"/>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="13"/>
-      <c r="AW4" s="13"/>
-      <c r="AX4" s="13"/>
-      <c r="AY4" s="13"/>
-      <c r="AZ4" s="13"/>
-      <c r="BA4" s="13"/>
-      <c r="BB4" s="13"/>
-      <c r="BC4" s="13"/>
-      <c r="BD4" s="13"/>
-      <c r="BE4" s="13"/>
-      <c r="BF4" s="13"/>
-      <c r="BG4" s="13"/>
-      <c r="BH4" s="13"/>
-      <c r="BI4" s="13"/>
-      <c r="BJ4" s="13"/>
-      <c r="BK4" s="13"/>
-      <c r="BL4" s="13"/>
-      <c r="BM4" s="13"/>
-      <c r="BN4" s="13"/>
-      <c r="BO4" s="13"/>
-      <c r="BP4" s="13"/>
-      <c r="BQ4" s="13"/>
-      <c r="BR4" s="13"/>
-      <c r="BS4" s="13"/>
-      <c r="BT4" s="13"/>
-      <c r="BU4" s="13"/>
-      <c r="BV4" s="13"/>
-      <c r="BW4" s="13"/>
-      <c r="BX4" s="13"/>
-      <c r="BY4" s="13"/>
-      <c r="BZ4" s="13"/>
-      <c r="CA4" s="13"/>
-      <c r="CB4" s="13"/>
-      <c r="CC4" s="13"/>
-      <c r="CD4" s="13"/>
-      <c r="CE4" s="13"/>
-      <c r="CF4" s="13"/>
-      <c r="CG4" s="13"/>
-      <c r="CH4" s="13"/>
-      <c r="CI4" s="13"/>
-      <c r="CJ4" s="13"/>
-      <c r="CK4" s="13"/>
-      <c r="CL4" s="13"/>
-      <c r="CM4" s="13"/>
-      <c r="CN4" s="13"/>
-      <c r="CO4" s="13"/>
-      <c r="CP4" s="13"/>
-      <c r="CQ4" s="13"/>
-      <c r="CR4" s="13"/>
-      <c r="CS4" s="13"/>
-      <c r="CT4" s="13"/>
-      <c r="CU4" s="13"/>
-      <c r="CV4" s="13"/>
-      <c r="CW4" s="13"/>
-      <c r="CX4" s="13"/>
-      <c r="CY4" s="13"/>
-      <c r="CZ4" s="13"/>
-      <c r="DA4" s="13"/>
-      <c r="DB4" s="13"/>
-      <c r="DC4" s="13"/>
-      <c r="DD4" s="13"/>
-      <c r="DE4" s="13"/>
-      <c r="DF4" s="13"/>
-      <c r="DG4" s="13"/>
-      <c r="DH4" s="13"/>
-      <c r="DI4" s="13"/>
-      <c r="DJ4" s="13"/>
-      <c r="DK4" s="13"/>
-      <c r="DL4" s="13"/>
-      <c r="DM4" s="13"/>
-      <c r="DN4" s="13"/>
-      <c r="DO4" s="13"/>
-      <c r="DP4" s="13"/>
-      <c r="DQ4" s="13"/>
-      <c r="DR4" s="13"/>
-      <c r="DS4" s="13"/>
-      <c r="DT4" s="13"/>
-      <c r="DU4" s="13"/>
-      <c r="DV4" s="13"/>
-      <c r="DW4" s="13"/>
-      <c r="DX4" s="13"/>
-      <c r="DY4" s="13"/>
-      <c r="DZ4" s="13"/>
-      <c r="EA4" s="13"/>
-      <c r="EB4" s="13"/>
-      <c r="EC4" s="13"/>
-      <c r="ED4" s="13"/>
-      <c r="EE4" s="13"/>
-      <c r="EF4" s="13"/>
-      <c r="EG4" s="13"/>
-      <c r="EH4" s="13"/>
-      <c r="EI4" s="13"/>
-      <c r="EJ4" s="13"/>
-      <c r="EK4" s="13"/>
-    </row>
-    <row r="5" spans="1:141" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="45" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
+      <c r="AI4" s="12"/>
+      <c r="AJ4" s="12"/>
+      <c r="AK4" s="12"/>
+      <c r="AL4" s="12"/>
+      <c r="AM4" s="12"/>
+      <c r="AN4" s="12"/>
+      <c r="AO4" s="12"/>
+      <c r="AP4" s="12"/>
+      <c r="AQ4" s="12"/>
+      <c r="AR4" s="12"/>
+      <c r="AS4" s="12"/>
+      <c r="AT4" s="12"/>
+      <c r="AU4" s="12"/>
+      <c r="AV4" s="12"/>
+      <c r="AW4" s="12"/>
+      <c r="AX4" s="12"/>
+      <c r="AY4" s="12"/>
+      <c r="AZ4" s="12"/>
+      <c r="BA4" s="12"/>
+      <c r="BB4" s="12"/>
+      <c r="BC4" s="12"/>
+      <c r="BD4" s="12"/>
+      <c r="BE4" s="12"/>
+      <c r="BF4" s="12"/>
+      <c r="BG4" s="12"/>
+      <c r="BH4" s="12"/>
+      <c r="BI4" s="12"/>
+      <c r="BJ4" s="12"/>
+      <c r="BK4" s="12"/>
+      <c r="BL4" s="12"/>
+      <c r="BM4" s="12"/>
+      <c r="BN4" s="12"/>
+      <c r="BO4" s="12"/>
+      <c r="BP4" s="12"/>
+      <c r="BQ4" s="12"/>
+      <c r="BR4" s="12"/>
+      <c r="BS4" s="12"/>
+      <c r="BT4" s="12"/>
+      <c r="BU4" s="12"/>
+      <c r="BV4" s="12"/>
+      <c r="BW4" s="12"/>
+      <c r="BX4" s="12"/>
+      <c r="BY4" s="12"/>
+      <c r="BZ4" s="12"/>
+      <c r="CA4" s="12"/>
+      <c r="CB4" s="12"/>
+      <c r="CC4" s="12"/>
+      <c r="CD4" s="12"/>
+      <c r="CE4" s="12"/>
+      <c r="CF4" s="12"/>
+      <c r="CG4" s="12"/>
+      <c r="CH4" s="12"/>
+      <c r="CI4" s="12"/>
+      <c r="CJ4" s="12"/>
+      <c r="CK4" s="12"/>
+      <c r="CL4" s="12"/>
+      <c r="CM4" s="12"/>
+      <c r="CN4" s="12"/>
+      <c r="CO4" s="12"/>
+      <c r="CP4" s="12"/>
+      <c r="CQ4" s="12"/>
+      <c r="CR4" s="12"/>
+      <c r="CS4" s="12"/>
+      <c r="CT4" s="12"/>
+      <c r="CU4" s="12"/>
+      <c r="CV4" s="12"/>
+      <c r="CW4" s="12"/>
+      <c r="CX4" s="12"/>
+      <c r="CY4" s="12"/>
+      <c r="CZ4" s="12"/>
+      <c r="DA4" s="12"/>
+      <c r="DB4" s="12"/>
+      <c r="DC4" s="12"/>
+      <c r="DD4" s="12"/>
+      <c r="DE4" s="12"/>
+      <c r="DF4" s="12"/>
+      <c r="DG4" s="12"/>
+      <c r="DH4" s="12"/>
+      <c r="DI4" s="12"/>
+      <c r="DJ4" s="12"/>
+      <c r="DK4" s="12"/>
+      <c r="DL4" s="12"/>
+      <c r="DM4" s="12"/>
+      <c r="DN4" s="12"/>
+      <c r="DO4" s="12"/>
+      <c r="DP4" s="12"/>
+      <c r="DQ4" s="12"/>
+      <c r="DR4" s="12"/>
+      <c r="DS4" s="12"/>
+      <c r="DT4" s="12"/>
+      <c r="DU4" s="12"/>
+      <c r="DV4" s="12"/>
+    </row>
+    <row r="5" spans="1:126" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="45" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45" t="s">
+      <c r="D5" s="47"/>
+      <c r="E5" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45" t="s">
+      <c r="F5" s="47"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="15"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="16"/>
-      <c r="Z5" s="16"/>
-      <c r="AA5" s="16"/>
-      <c r="AB5" s="16"/>
-      <c r="AC5" s="16"/>
-      <c r="AD5" s="16"/>
-      <c r="AE5" s="16"/>
-      <c r="AF5" s="16"/>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="16"/>
-      <c r="AI5" s="16"/>
-      <c r="AJ5" s="16"/>
-      <c r="AK5" s="16"/>
-      <c r="AL5" s="16"/>
-      <c r="AM5" s="16"/>
-      <c r="AN5" s="16"/>
-      <c r="AO5" s="16"/>
-      <c r="AP5" s="16"/>
-      <c r="AQ5" s="16"/>
-      <c r="AR5" s="16"/>
-      <c r="AS5" s="16"/>
-      <c r="AT5" s="16"/>
-      <c r="AU5" s="16"/>
-      <c r="AV5" s="16"/>
-      <c r="AW5" s="16"/>
-      <c r="AX5" s="16"/>
-      <c r="AY5" s="16"/>
-      <c r="AZ5" s="16"/>
-      <c r="BA5" s="16"/>
-      <c r="BB5" s="16"/>
-      <c r="BC5" s="16"/>
-      <c r="BD5" s="16"/>
-      <c r="BE5" s="16"/>
-      <c r="BF5" s="16"/>
-      <c r="BG5" s="16"/>
-      <c r="BH5" s="16"/>
-      <c r="BI5" s="16"/>
-      <c r="BJ5" s="16"/>
-      <c r="BK5" s="16"/>
-      <c r="BL5" s="16"/>
-      <c r="BM5" s="16"/>
-      <c r="BN5" s="16"/>
-      <c r="BO5" s="16"/>
-      <c r="BP5" s="16"/>
-      <c r="BQ5" s="16"/>
-      <c r="BR5" s="16"/>
-      <c r="BS5" s="16"/>
-      <c r="BT5" s="16"/>
-      <c r="BU5" s="16"/>
-      <c r="BV5" s="16"/>
-      <c r="BW5" s="16"/>
-      <c r="BX5" s="16"/>
-      <c r="BY5" s="16"/>
-      <c r="BZ5" s="16"/>
-      <c r="CA5" s="16"/>
-      <c r="CB5" s="16"/>
-      <c r="CC5" s="16"/>
-      <c r="CD5" s="16"/>
-      <c r="CE5" s="16"/>
-      <c r="CF5" s="16"/>
-      <c r="CG5" s="16"/>
-      <c r="CH5" s="16"/>
-      <c r="CI5" s="16"/>
-      <c r="CJ5" s="16"/>
-      <c r="CK5" s="16"/>
-      <c r="CL5" s="16"/>
-      <c r="CM5" s="16"/>
-      <c r="CN5" s="16"/>
-      <c r="CO5" s="16"/>
-      <c r="CP5" s="16"/>
-      <c r="CQ5" s="16"/>
-      <c r="CR5" s="16"/>
-      <c r="CS5" s="16"/>
-      <c r="CT5" s="16"/>
-      <c r="CU5" s="16"/>
-      <c r="CV5" s="16"/>
-      <c r="CW5" s="16"/>
-      <c r="CX5" s="16"/>
-      <c r="CY5" s="16"/>
-      <c r="CZ5" s="16"/>
-      <c r="DA5" s="16"/>
-      <c r="DB5" s="16"/>
-      <c r="DC5" s="16"/>
-      <c r="DD5" s="16"/>
-      <c r="DE5" s="16"/>
-      <c r="DF5" s="16"/>
-      <c r="DG5" s="16"/>
-      <c r="DH5" s="16"/>
-      <c r="DI5" s="16"/>
-      <c r="DJ5" s="16"/>
-      <c r="DK5" s="16"/>
-      <c r="DL5" s="16"/>
-      <c r="DM5" s="16"/>
-      <c r="DN5" s="16"/>
-      <c r="DO5" s="16"/>
-      <c r="DP5" s="16"/>
-      <c r="DQ5" s="16"/>
-      <c r="DR5" s="16"/>
-      <c r="DS5" s="16"/>
-      <c r="DT5" s="16"/>
-      <c r="DU5" s="16"/>
-      <c r="DV5" s="16"/>
-      <c r="DW5" s="16"/>
-      <c r="DX5" s="16"/>
-      <c r="DY5" s="16"/>
-      <c r="DZ5" s="16"/>
-      <c r="EA5" s="16"/>
-      <c r="EB5" s="16"/>
-      <c r="EC5" s="16"/>
-      <c r="ED5" s="16"/>
-      <c r="EE5" s="16"/>
-      <c r="EF5" s="16"/>
-      <c r="EG5" s="16"/>
-      <c r="EH5" s="16"/>
-      <c r="EI5" s="16"/>
-      <c r="EJ5" s="16"/>
-      <c r="EK5" s="16"/>
-    </row>
-    <row r="6" spans="1:141" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="17"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="13"/>
-      <c r="AO6" s="13"/>
-      <c r="AP6" s="13"/>
-      <c r="AQ6" s="13"/>
-      <c r="AR6" s="13"/>
-      <c r="AS6" s="13"/>
-      <c r="AT6" s="13"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="13"/>
-      <c r="AX6" s="13"/>
-      <c r="AY6" s="13"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="13"/>
-      <c r="BB6" s="13"/>
-      <c r="BC6" s="13"/>
-      <c r="BD6" s="13"/>
-      <c r="BE6" s="13"/>
-      <c r="BF6" s="13"/>
-      <c r="BG6" s="13"/>
-      <c r="BH6" s="13"/>
-      <c r="BI6" s="13"/>
-      <c r="BJ6" s="13"/>
-      <c r="BK6" s="13"/>
-      <c r="BL6" s="13"/>
-      <c r="BM6" s="13"/>
-      <c r="BN6" s="13"/>
-      <c r="BO6" s="13"/>
-      <c r="BP6" s="13"/>
-      <c r="BQ6" s="13"/>
-      <c r="BR6" s="13"/>
-      <c r="BS6" s="13"/>
-      <c r="BT6" s="13"/>
-      <c r="BU6" s="13"/>
-      <c r="BV6" s="13"/>
-      <c r="BW6" s="13"/>
-      <c r="BX6" s="13"/>
-      <c r="BY6" s="13"/>
-      <c r="BZ6" s="13"/>
-      <c r="CA6" s="13"/>
-      <c r="CB6" s="13"/>
-      <c r="CC6" s="13"/>
-      <c r="CD6" s="13"/>
-      <c r="CE6" s="13"/>
-      <c r="CF6" s="13"/>
-      <c r="CG6" s="13"/>
-      <c r="CH6" s="13"/>
-      <c r="CI6" s="13"/>
-      <c r="CJ6" s="13"/>
-      <c r="CK6" s="13"/>
-      <c r="CL6" s="13"/>
-      <c r="CM6" s="13"/>
-      <c r="CN6" s="13"/>
-      <c r="CO6" s="13"/>
-      <c r="CP6" s="13"/>
-      <c r="CQ6" s="13"/>
-      <c r="CR6" s="13"/>
-      <c r="CS6" s="13"/>
-      <c r="CT6" s="13"/>
-      <c r="CU6" s="13"/>
-      <c r="CV6" s="13"/>
-      <c r="CW6" s="13"/>
-      <c r="CX6" s="13"/>
-      <c r="CY6" s="13"/>
-      <c r="CZ6" s="13"/>
-      <c r="DA6" s="13"/>
-      <c r="DB6" s="13"/>
-      <c r="DC6" s="13"/>
-      <c r="DD6" s="13"/>
-      <c r="DE6" s="13"/>
-      <c r="DF6" s="13"/>
-      <c r="DG6" s="13"/>
-      <c r="DH6" s="13"/>
-      <c r="DI6" s="13"/>
-      <c r="DJ6" s="13"/>
-      <c r="DK6" s="13"/>
-      <c r="DL6" s="13"/>
-      <c r="DM6" s="13"/>
-      <c r="DN6" s="13"/>
-      <c r="DO6" s="13"/>
-      <c r="DP6" s="13"/>
-      <c r="DQ6" s="13"/>
-      <c r="DR6" s="13"/>
-      <c r="DS6" s="13"/>
-      <c r="DT6" s="13"/>
-      <c r="DU6" s="13"/>
-      <c r="DV6" s="13"/>
-      <c r="DW6" s="13"/>
-      <c r="DX6" s="13"/>
-      <c r="DY6" s="13"/>
-      <c r="DZ6" s="13"/>
-      <c r="EA6" s="13"/>
-      <c r="EB6" s="13"/>
-      <c r="EC6" s="13"/>
-      <c r="ED6" s="13"/>
-      <c r="EE6" s="13"/>
-      <c r="EF6" s="13"/>
-      <c r="EG6" s="13"/>
-      <c r="EH6" s="13"/>
-      <c r="EI6" s="13"/>
-      <c r="EJ6" s="13"/>
-      <c r="EK6" s="13"/>
-    </row>
-    <row r="7" spans="1:141" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-    </row>
-    <row r="8" spans="1:141" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-    </row>
-    <row r="9" spans="1:141" s="13" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14"/>
+      <c r="AI5" s="14"/>
+      <c r="AJ5" s="14"/>
+      <c r="AK5" s="14"/>
+      <c r="AL5" s="14"/>
+      <c r="AM5" s="14"/>
+      <c r="AN5" s="14"/>
+      <c r="AO5" s="14"/>
+      <c r="AP5" s="14"/>
+      <c r="AQ5" s="14"/>
+      <c r="AR5" s="14"/>
+      <c r="AS5" s="14"/>
+      <c r="AT5" s="14"/>
+      <c r="AU5" s="14"/>
+      <c r="AV5" s="14"/>
+      <c r="AW5" s="14"/>
+      <c r="AX5" s="14"/>
+      <c r="AY5" s="14"/>
+      <c r="AZ5" s="14"/>
+      <c r="BA5" s="14"/>
+      <c r="BB5" s="14"/>
+      <c r="BC5" s="14"/>
+      <c r="BD5" s="14"/>
+      <c r="BE5" s="14"/>
+      <c r="BF5" s="14"/>
+      <c r="BG5" s="14"/>
+      <c r="BH5" s="14"/>
+      <c r="BI5" s="14"/>
+      <c r="BJ5" s="14"/>
+      <c r="BK5" s="14"/>
+      <c r="BL5" s="14"/>
+      <c r="BM5" s="14"/>
+      <c r="BN5" s="14"/>
+      <c r="BO5" s="14"/>
+      <c r="BP5" s="14"/>
+      <c r="BQ5" s="14"/>
+      <c r="BR5" s="14"/>
+      <c r="BS5" s="14"/>
+      <c r="BT5" s="14"/>
+      <c r="BU5" s="14"/>
+      <c r="BV5" s="14"/>
+      <c r="BW5" s="14"/>
+      <c r="BX5" s="14"/>
+      <c r="BY5" s="14"/>
+      <c r="BZ5" s="14"/>
+      <c r="CA5" s="14"/>
+      <c r="CB5" s="14"/>
+      <c r="CC5" s="14"/>
+      <c r="CD5" s="14"/>
+      <c r="CE5" s="14"/>
+      <c r="CF5" s="14"/>
+      <c r="CG5" s="14"/>
+      <c r="CH5" s="14"/>
+      <c r="CI5" s="14"/>
+      <c r="CJ5" s="14"/>
+      <c r="CK5" s="14"/>
+      <c r="CL5" s="14"/>
+      <c r="CM5" s="14"/>
+      <c r="CN5" s="14"/>
+      <c r="CO5" s="14"/>
+      <c r="CP5" s="14"/>
+      <c r="CQ5" s="14"/>
+      <c r="CR5" s="14"/>
+      <c r="CS5" s="14"/>
+      <c r="CT5" s="14"/>
+      <c r="CU5" s="14"/>
+      <c r="CV5" s="14"/>
+      <c r="CW5" s="14"/>
+      <c r="CX5" s="14"/>
+      <c r="CY5" s="14"/>
+      <c r="CZ5" s="14"/>
+      <c r="DA5" s="14"/>
+      <c r="DB5" s="14"/>
+      <c r="DC5" s="14"/>
+      <c r="DD5" s="14"/>
+      <c r="DE5" s="14"/>
+      <c r="DF5" s="14"/>
+      <c r="DG5" s="14"/>
+      <c r="DH5" s="14"/>
+      <c r="DI5" s="14"/>
+      <c r="DJ5" s="14"/>
+      <c r="DK5" s="14"/>
+      <c r="DL5" s="14"/>
+      <c r="DM5" s="14"/>
+      <c r="DN5" s="14"/>
+      <c r="DO5" s="14"/>
+      <c r="DP5" s="14"/>
+      <c r="DQ5" s="14"/>
+      <c r="DR5" s="14"/>
+      <c r="DS5" s="14"/>
+      <c r="DT5" s="14"/>
+      <c r="DU5" s="14"/>
+      <c r="DV5" s="14"/>
+    </row>
+    <row r="6" spans="1:126" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="32"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="12"/>
+      <c r="AG6" s="12"/>
+      <c r="AH6" s="12"/>
+      <c r="AI6" s="12"/>
+      <c r="AJ6" s="12"/>
+      <c r="AK6" s="12"/>
+      <c r="AL6" s="12"/>
+      <c r="AM6" s="12"/>
+      <c r="AN6" s="12"/>
+      <c r="AO6" s="12"/>
+      <c r="AP6" s="12"/>
+      <c r="AQ6" s="12"/>
+      <c r="AR6" s="12"/>
+      <c r="AS6" s="12"/>
+      <c r="AT6" s="12"/>
+      <c r="AU6" s="12"/>
+      <c r="AV6" s="12"/>
+      <c r="AW6" s="12"/>
+      <c r="AX6" s="12"/>
+      <c r="AY6" s="12"/>
+      <c r="AZ6" s="12"/>
+      <c r="BA6" s="12"/>
+      <c r="BB6" s="12"/>
+      <c r="BC6" s="12"/>
+      <c r="BD6" s="12"/>
+      <c r="BE6" s="12"/>
+      <c r="BF6" s="12"/>
+      <c r="BG6" s="12"/>
+      <c r="BH6" s="12"/>
+      <c r="BI6" s="12"/>
+      <c r="BJ6" s="12"/>
+      <c r="BK6" s="12"/>
+      <c r="BL6" s="12"/>
+      <c r="BM6" s="12"/>
+      <c r="BN6" s="12"/>
+      <c r="BO6" s="12"/>
+      <c r="BP6" s="12"/>
+      <c r="BQ6" s="12"/>
+      <c r="BR6" s="12"/>
+      <c r="BS6" s="12"/>
+      <c r="BT6" s="12"/>
+      <c r="BU6" s="12"/>
+      <c r="BV6" s="12"/>
+      <c r="BW6" s="12"/>
+      <c r="BX6" s="12"/>
+      <c r="BY6" s="12"/>
+      <c r="BZ6" s="12"/>
+      <c r="CA6" s="12"/>
+      <c r="CB6" s="12"/>
+      <c r="CC6" s="12"/>
+      <c r="CD6" s="12"/>
+      <c r="CE6" s="12"/>
+      <c r="CF6" s="12"/>
+      <c r="CG6" s="12"/>
+      <c r="CH6" s="12"/>
+      <c r="CI6" s="12"/>
+      <c r="CJ6" s="12"/>
+      <c r="CK6" s="12"/>
+      <c r="CL6" s="12"/>
+      <c r="CM6" s="12"/>
+      <c r="CN6" s="12"/>
+      <c r="CO6" s="12"/>
+      <c r="CP6" s="12"/>
+      <c r="CQ6" s="12"/>
+      <c r="CR6" s="12"/>
+      <c r="CS6" s="12"/>
+      <c r="CT6" s="12"/>
+      <c r="CU6" s="12"/>
+      <c r="CV6" s="12"/>
+      <c r="CW6" s="12"/>
+      <c r="CX6" s="12"/>
+      <c r="CY6" s="12"/>
+      <c r="CZ6" s="12"/>
+      <c r="DA6" s="12"/>
+      <c r="DB6" s="12"/>
+      <c r="DC6" s="12"/>
+      <c r="DD6" s="12"/>
+      <c r="DE6" s="12"/>
+      <c r="DF6" s="12"/>
+      <c r="DG6" s="12"/>
+      <c r="DH6" s="12"/>
+      <c r="DI6" s="12"/>
+      <c r="DJ6" s="12"/>
+      <c r="DK6" s="12"/>
+      <c r="DL6" s="12"/>
+      <c r="DM6" s="12"/>
+      <c r="DN6" s="12"/>
+      <c r="DO6" s="12"/>
+      <c r="DP6" s="12"/>
+      <c r="DQ6" s="12"/>
+      <c r="DR6" s="12"/>
+      <c r="DS6" s="12"/>
+      <c r="DT6" s="12"/>
+      <c r="DU6" s="12"/>
+      <c r="DV6" s="12"/>
+    </row>
+    <row r="7" spans="1:126" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="32"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+    </row>
+    <row r="8" spans="1:126" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="32"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+    </row>
+    <row r="9" spans="1:126" s="12" customFormat="1" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="15"/>
+      <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="19"/>
-    </row>
-    <row r="10" spans="1:141" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
-        <v>416</v>
-      </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="42" t="s">
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:126" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="B10" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="42"/>
-      <c r="F10" s="30" t="s">
+      <c r="C10" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="D10" s="19" t="s">
+        <v>827</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>825</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>826</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>829</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>830</v>
+      </c>
+      <c r="I10" s="18" t="s">
         <v>831</v>
       </c>
-      <c r="H10" s="21" t="s">
-        <v>828</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>829</v>
-      </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:126" s="12" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="38"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="21"/>
+      <c r="F11" s="30" t="s">
         <v>832</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>830</v>
-      </c>
-      <c r="L10" s="22"/>
-      <c r="M10" s="42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:141" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="I11" s="40" t="s">
-        <v>417</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>418</v>
-      </c>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="43"/>
-    </row>
-    <row r="12" spans="1:141" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
-    </row>
-    <row r="13" spans="1:141" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-    </row>
-    <row r="14" spans="1:141" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-    </row>
-    <row r="15" spans="1:141" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-    </row>
-    <row r="16" spans="1:141" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-    </row>
-    <row r="17" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-    </row>
-    <row r="18" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="32"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-    </row>
-    <row r="19" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="32"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-    </row>
-    <row r="20" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="32"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-    </row>
-    <row r="21" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-    </row>
-    <row r="22" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-    </row>
-    <row r="23" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-    </row>
-    <row r="24" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-    </row>
-    <row r="25" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-    </row>
-    <row r="26" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-    </row>
-    <row r="27" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="32"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-    </row>
-    <row r="28" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="32"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-    </row>
-    <row r="29" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-    </row>
-    <row r="30" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-    </row>
-    <row r="31" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
-    </row>
-    <row r="32" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
-      <c r="M32" s="32"/>
-    </row>
-    <row r="33" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="32"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-    </row>
-    <row r="34" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-    </row>
-    <row r="35" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="32"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
-    </row>
-    <row r="36" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-    </row>
-    <row r="37" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
-      <c r="M37" s="32"/>
-    </row>
-    <row r="38" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="32"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
-      <c r="M38" s="32"/>
-    </row>
-    <row r="39" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="32"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
-    </row>
-    <row r="40" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="32"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
-    </row>
-    <row r="41" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="32"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
-    </row>
-    <row r="42" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="32"/>
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="32"/>
-    </row>
-    <row r="43" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="32"/>
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
-      <c r="L43" s="32"/>
-      <c r="M43" s="32"/>
-    </row>
-    <row r="44" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="32"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="32"/>
-      <c r="L44" s="32"/>
-      <c r="M44" s="32"/>
-    </row>
-    <row r="45" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="32"/>
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
-      <c r="M45" s="32"/>
-    </row>
-    <row r="46" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="32"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="32"/>
-      <c r="L46" s="32"/>
-      <c r="M46" s="32"/>
-    </row>
-    <row r="47" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="32"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
-      <c r="M47" s="32"/>
-    </row>
-    <row r="48" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="32"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="32"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="32"/>
-      <c r="L48" s="32"/>
-      <c r="M48" s="32"/>
-    </row>
-    <row r="49" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="32"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="32"/>
-      <c r="L49" s="32"/>
-      <c r="M49" s="32"/>
-    </row>
-    <row r="50" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="32"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="32"/>
-      <c r="L50" s="32"/>
-      <c r="M50" s="32"/>
-    </row>
-    <row r="51" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="32"/>
-      <c r="B51" s="32"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
-      <c r="M51" s="32"/>
-    </row>
-    <row r="52" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="32"/>
-      <c r="B52" s="32"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="32"/>
-      <c r="L52" s="32"/>
-      <c r="M52" s="32"/>
-    </row>
-    <row r="53" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="32"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="32"/>
-      <c r="L53" s="32"/>
-      <c r="M53" s="32"/>
-    </row>
-    <row r="54" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="32"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="32"/>
-      <c r="L54" s="32"/>
-      <c r="M54" s="32"/>
-    </row>
-    <row r="55" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="32"/>
-      <c r="B55" s="32"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="32"/>
-      <c r="L55" s="32"/>
-      <c r="M55" s="32"/>
-    </row>
-    <row r="56" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="32"/>
-      <c r="B56" s="32"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="32"/>
-      <c r="L56" s="32"/>
-      <c r="M56" s="32"/>
-    </row>
-    <row r="57" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="32"/>
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="32"/>
-      <c r="L57" s="32"/>
-      <c r="M57" s="32"/>
-    </row>
-    <row r="58" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="32"/>
-      <c r="B58" s="32"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="32"/>
-      <c r="L58" s="32"/>
-      <c r="M58" s="32"/>
-    </row>
-    <row r="59" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="32"/>
-      <c r="B59" s="32"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32"/>
-      <c r="L59" s="32"/>
-      <c r="M59" s="32"/>
-    </row>
-    <row r="60" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="32"/>
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="32"/>
-      <c r="L60" s="32"/>
-      <c r="M60" s="32"/>
-    </row>
-    <row r="61" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="32"/>
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="32"/>
-      <c r="L61" s="32"/>
-      <c r="M61" s="32"/>
-    </row>
-    <row r="62" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="32"/>
-      <c r="B62" s="32"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="32"/>
-      <c r="L62" s="32"/>
-      <c r="M62" s="32"/>
-    </row>
-    <row r="63" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="32"/>
-      <c r="B63" s="32"/>
-      <c r="C63" s="32"/>
-      <c r="D63" s="48"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="32"/>
-      <c r="K63" s="32"/>
-      <c r="L63" s="32"/>
-      <c r="M63" s="32"/>
-    </row>
-    <row r="64" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="32"/>
-      <c r="B64" s="32"/>
-      <c r="C64" s="32"/>
-      <c r="D64" s="48"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="32"/>
-      <c r="K64" s="32"/>
-      <c r="L64" s="32"/>
-      <c r="M64" s="32"/>
-    </row>
-    <row r="65" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="32"/>
-      <c r="B65" s="32"/>
-      <c r="C65" s="32"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="32"/>
-      <c r="J65" s="32"/>
-      <c r="K65" s="32"/>
-      <c r="L65" s="32"/>
-      <c r="M65" s="32"/>
-    </row>
-    <row r="66" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="32"/>
-      <c r="B66" s="32"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="48"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="32"/>
-      <c r="I66" s="32"/>
-      <c r="J66" s="32"/>
-      <c r="K66" s="32"/>
-      <c r="L66" s="32"/>
-      <c r="M66" s="32"/>
-    </row>
-    <row r="67" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="32"/>
-      <c r="B67" s="32"/>
-      <c r="C67" s="32"/>
-      <c r="D67" s="48"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="32"/>
-      <c r="J67" s="32"/>
-      <c r="K67" s="32"/>
-      <c r="L67" s="32"/>
-      <c r="M67" s="32"/>
-    </row>
-    <row r="68" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="32"/>
-      <c r="B68" s="32"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="32"/>
-      <c r="L68" s="32"/>
-      <c r="M68" s="32"/>
-    </row>
-    <row r="69" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="32"/>
-      <c r="B69" s="32"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="32"/>
-      <c r="L69" s="32"/>
-      <c r="M69" s="32"/>
-    </row>
-    <row r="70" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="32"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="32"/>
-      <c r="L70" s="32"/>
-      <c r="M70" s="32"/>
-    </row>
-    <row r="71" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="32"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="32"/>
-      <c r="M71" s="32"/>
-    </row>
-    <row r="72" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="32"/>
-      <c r="B72" s="32"/>
-      <c r="C72" s="32"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="32"/>
-      <c r="L72" s="32"/>
-      <c r="M72" s="32"/>
-    </row>
-    <row r="73" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="32"/>
-      <c r="B73" s="32"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="48"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="32"/>
-      <c r="L73" s="32"/>
-      <c r="M73" s="32"/>
-    </row>
-    <row r="74" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="32"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="32"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="32"/>
-      <c r="J74" s="32"/>
-      <c r="K74" s="32"/>
-      <c r="L74" s="32"/>
-      <c r="M74" s="32"/>
-    </row>
-    <row r="75" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="32"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
-      <c r="J75" s="32"/>
-      <c r="K75" s="32"/>
-      <c r="L75" s="32"/>
-      <c r="M75" s="32"/>
-    </row>
-    <row r="76" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="32"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
-      <c r="J76" s="32"/>
-      <c r="K76" s="32"/>
-      <c r="L76" s="32"/>
-      <c r="M76" s="32"/>
-    </row>
-    <row r="77" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="32"/>
-      <c r="B77" s="32"/>
-      <c r="C77" s="32"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="48"/>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="32"/>
-      <c r="J77" s="32"/>
-      <c r="K77" s="32"/>
-      <c r="L77" s="32"/>
-      <c r="M77" s="32"/>
-    </row>
-    <row r="78" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="32"/>
-      <c r="B78" s="32"/>
-      <c r="C78" s="32"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="32"/>
-      <c r="I78" s="32"/>
-      <c r="J78" s="32"/>
-      <c r="K78" s="32"/>
-      <c r="L78" s="32"/>
-      <c r="M78" s="32"/>
-    </row>
-    <row r="79" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="32"/>
-      <c r="B79" s="32"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
-      <c r="J79" s="32"/>
-      <c r="K79" s="32"/>
-      <c r="L79" s="32"/>
-      <c r="M79" s="32"/>
-    </row>
-    <row r="80" spans="1:13" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="32"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
-      <c r="J80" s="32"/>
-      <c r="K80" s="32"/>
-      <c r="L80" s="32"/>
-      <c r="M80" s="32"/>
-    </row>
-    <row r="81" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="25"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="33"/>
-      <c r="D81" s="49"/>
-      <c r="E81" s="49"/>
-      <c r="F81" s="33"/>
-      <c r="G81" s="33"/>
-      <c r="H81" s="25"/>
-      <c r="I81" s="33"/>
-      <c r="J81" s="33"/>
-      <c r="K81" s="33"/>
-      <c r="L81" s="33"/>
-      <c r="M81" s="25"/>
-    </row>
-    <row r="82" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="25"/>
-      <c r="B82" s="25"/>
-      <c r="C82" s="33"/>
-      <c r="D82" s="49"/>
-      <c r="E82" s="49"/>
-      <c r="F82" s="33"/>
-      <c r="G82" s="33"/>
-      <c r="H82" s="25"/>
-      <c r="I82" s="33"/>
-      <c r="J82" s="33"/>
-      <c r="K82" s="33"/>
-      <c r="L82" s="33"/>
-      <c r="M82" s="25"/>
-    </row>
-    <row r="83" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="25"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="33"/>
-      <c r="D83" s="49"/>
-      <c r="E83" s="49"/>
-      <c r="F83" s="33"/>
-      <c r="G83" s="33"/>
-      <c r="H83" s="25"/>
-      <c r="I83" s="33"/>
-      <c r="J83" s="33"/>
-      <c r="K83" s="33"/>
-      <c r="L83" s="33"/>
-      <c r="M83" s="25"/>
-    </row>
-    <row r="84" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="25"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="33"/>
-      <c r="D84" s="49"/>
-      <c r="E84" s="49"/>
-      <c r="F84" s="33"/>
-      <c r="G84" s="33"/>
-      <c r="H84" s="25"/>
-      <c r="I84" s="33"/>
-      <c r="J84" s="33"/>
-      <c r="K84" s="33"/>
-      <c r="L84" s="33"/>
-      <c r="M84" s="25"/>
-    </row>
-    <row r="85" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="25"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="33"/>
-      <c r="D85" s="49"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="33"/>
-      <c r="G85" s="33"/>
-      <c r="H85" s="25"/>
-      <c r="I85" s="33"/>
-      <c r="J85" s="33"/>
-      <c r="K85" s="33"/>
-      <c r="L85" s="33"/>
-      <c r="M85" s="25"/>
-    </row>
-    <row r="86" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="25"/>
-      <c r="B86" s="25"/>
-      <c r="C86" s="33"/>
-      <c r="D86" s="49"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="33"/>
-      <c r="G86" s="33"/>
-      <c r="H86" s="25"/>
-      <c r="I86" s="33"/>
-      <c r="J86" s="33"/>
-      <c r="K86" s="33"/>
-      <c r="L86" s="33"/>
-      <c r="M86" s="25"/>
-    </row>
-    <row r="87" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="25"/>
-      <c r="B87" s="25"/>
-      <c r="C87" s="33"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="33"/>
-      <c r="G87" s="33"/>
-      <c r="H87" s="25"/>
-      <c r="I87" s="33"/>
-      <c r="J87" s="33"/>
-      <c r="K87" s="33"/>
-      <c r="L87" s="33"/>
-      <c r="M87" s="25"/>
-    </row>
-    <row r="88" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="25"/>
-      <c r="B88" s="25"/>
-      <c r="C88" s="33"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="33"/>
-      <c r="G88" s="33"/>
-      <c r="H88" s="25"/>
-      <c r="I88" s="33"/>
-      <c r="J88" s="33"/>
-      <c r="K88" s="33"/>
-      <c r="L88" s="33"/>
-      <c r="M88" s="25"/>
-    </row>
-    <row r="89" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="25"/>
-      <c r="B89" s="25"/>
-      <c r="C89" s="33"/>
-      <c r="D89" s="49"/>
-      <c r="E89" s="49"/>
-      <c r="F89" s="33"/>
-      <c r="G89" s="33"/>
-      <c r="H89" s="25"/>
-      <c r="I89" s="33"/>
-      <c r="J89" s="33"/>
-      <c r="K89" s="33"/>
-      <c r="L89" s="33"/>
-      <c r="M89" s="25"/>
-    </row>
-    <row r="90" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="25"/>
-      <c r="B90" s="25"/>
-      <c r="C90" s="33"/>
-      <c r="D90" s="49"/>
-      <c r="E90" s="49"/>
-      <c r="F90" s="33"/>
-      <c r="G90" s="33"/>
-      <c r="H90" s="25"/>
-      <c r="I90" s="33"/>
-      <c r="J90" s="33"/>
-      <c r="K90" s="33"/>
-      <c r="L90" s="33"/>
-      <c r="M90" s="25"/>
-    </row>
-    <row r="91" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="25"/>
-      <c r="B91" s="25"/>
-      <c r="C91" s="33"/>
-      <c r="D91" s="49"/>
-      <c r="E91" s="49"/>
-      <c r="F91" s="33"/>
-      <c r="G91" s="33"/>
-      <c r="H91" s="25"/>
-      <c r="I91" s="33"/>
-      <c r="J91" s="33"/>
-      <c r="K91" s="33"/>
-      <c r="L91" s="33"/>
-      <c r="M91" s="25"/>
-    </row>
-    <row r="92" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="25"/>
-      <c r="B92" s="25"/>
-      <c r="C92" s="33"/>
-      <c r="D92" s="49"/>
-      <c r="E92" s="49"/>
-      <c r="F92" s="33"/>
-      <c r="G92" s="33"/>
-      <c r="H92" s="25"/>
-      <c r="I92" s="33"/>
-      <c r="J92" s="33"/>
-      <c r="K92" s="33"/>
-      <c r="L92" s="33"/>
-      <c r="M92" s="25"/>
-    </row>
-    <row r="93" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="25"/>
-      <c r="B93" s="25"/>
-      <c r="C93" s="33"/>
-      <c r="D93" s="49"/>
-      <c r="E93" s="49"/>
-      <c r="F93" s="33"/>
-      <c r="G93" s="33"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="33"/>
-      <c r="J93" s="33"/>
-      <c r="K93" s="33"/>
-      <c r="L93" s="33"/>
-      <c r="M93" s="25"/>
-    </row>
-    <row r="94" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="25"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="33"/>
-      <c r="D94" s="49"/>
-      <c r="E94" s="49"/>
-      <c r="F94" s="33"/>
-      <c r="G94" s="33"/>
-      <c r="H94" s="25"/>
-      <c r="I94" s="33"/>
-      <c r="J94" s="33"/>
-      <c r="K94" s="33"/>
-      <c r="L94" s="33"/>
-      <c r="M94" s="25"/>
-    </row>
-    <row r="95" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="25"/>
-      <c r="B95" s="25"/>
-      <c r="C95" s="33"/>
-      <c r="D95" s="49"/>
-      <c r="E95" s="49"/>
-      <c r="F95" s="33"/>
-      <c r="G95" s="33"/>
-      <c r="H95" s="25"/>
-      <c r="I95" s="33"/>
-      <c r="J95" s="33"/>
-      <c r="K95" s="33"/>
-      <c r="L95" s="33"/>
-      <c r="M95" s="25"/>
-    </row>
-    <row r="96" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="25"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="33"/>
-      <c r="D96" s="49"/>
-      <c r="E96" s="49"/>
-      <c r="F96" s="33"/>
-      <c r="G96" s="33"/>
-      <c r="H96" s="25"/>
-      <c r="I96" s="33"/>
-      <c r="J96" s="33"/>
-      <c r="K96" s="33"/>
-      <c r="L96" s="33"/>
-      <c r="M96" s="25"/>
-    </row>
-    <row r="97" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="25"/>
-      <c r="B97" s="25"/>
-      <c r="C97" s="33"/>
-      <c r="D97" s="49"/>
-      <c r="E97" s="49"/>
-      <c r="F97" s="33"/>
-      <c r="G97" s="33"/>
-      <c r="H97" s="25"/>
-      <c r="I97" s="33"/>
-      <c r="J97" s="33"/>
-      <c r="K97" s="33"/>
-      <c r="L97" s="33"/>
-      <c r="M97" s="25"/>
-    </row>
-    <row r="98" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="25"/>
-      <c r="B98" s="25"/>
-      <c r="C98" s="33"/>
-      <c r="D98" s="49"/>
-      <c r="E98" s="49"/>
-      <c r="F98" s="33"/>
-      <c r="G98" s="33"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="33"/>
-      <c r="J98" s="33"/>
-      <c r="K98" s="33"/>
-      <c r="L98" s="33"/>
-      <c r="M98" s="25"/>
-    </row>
-    <row r="99" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="25"/>
-      <c r="B99" s="25"/>
-      <c r="C99" s="33"/>
-      <c r="D99" s="49"/>
-      <c r="E99" s="49"/>
-      <c r="F99" s="33"/>
-      <c r="G99" s="33"/>
-      <c r="H99" s="25"/>
-      <c r="I99" s="33"/>
-      <c r="J99" s="33"/>
-      <c r="K99" s="33"/>
-      <c r="L99" s="33"/>
-      <c r="M99" s="25"/>
-    </row>
-    <row r="100" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="25"/>
-      <c r="B100" s="25"/>
-      <c r="C100" s="33"/>
-      <c r="D100" s="49"/>
-      <c r="E100" s="49"/>
-      <c r="F100" s="33"/>
-      <c r="G100" s="33"/>
-      <c r="H100" s="25"/>
-      <c r="I100" s="33"/>
-      <c r="J100" s="33"/>
-      <c r="K100" s="33"/>
-      <c r="L100" s="33"/>
-      <c r="M100" s="25"/>
-    </row>
-    <row r="101" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="25"/>
-      <c r="B101" s="25"/>
-      <c r="C101" s="33"/>
-      <c r="D101" s="49"/>
-      <c r="E101" s="49"/>
-      <c r="F101" s="33"/>
-      <c r="G101" s="33"/>
-      <c r="H101" s="25"/>
-      <c r="I101" s="33"/>
-      <c r="J101" s="33"/>
-      <c r="K101" s="33"/>
-      <c r="L101" s="33"/>
-      <c r="M101" s="25"/>
-    </row>
-    <row r="102" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="25"/>
-      <c r="B102" s="25"/>
-      <c r="C102" s="33"/>
-      <c r="D102" s="49"/>
-      <c r="E102" s="49"/>
-      <c r="F102" s="33"/>
-      <c r="G102" s="33"/>
-      <c r="H102" s="25"/>
-      <c r="I102" s="33"/>
-      <c r="J102" s="33"/>
-      <c r="K102" s="33"/>
-      <c r="L102" s="33"/>
-      <c r="M102" s="25"/>
-    </row>
-    <row r="103" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="25"/>
-      <c r="B103" s="25"/>
-      <c r="C103" s="33"/>
-      <c r="D103" s="49"/>
-      <c r="E103" s="49"/>
-      <c r="F103" s="33"/>
-      <c r="G103" s="33"/>
-      <c r="H103" s="25"/>
-      <c r="I103" s="33"/>
-      <c r="J103" s="33"/>
-      <c r="K103" s="33"/>
-      <c r="L103" s="33"/>
-      <c r="M103" s="25"/>
-    </row>
-    <row r="104" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="25"/>
-      <c r="B104" s="25"/>
-      <c r="C104" s="33"/>
-      <c r="D104" s="49"/>
-      <c r="E104" s="49"/>
-      <c r="F104" s="33"/>
-      <c r="G104" s="33"/>
-      <c r="H104" s="25"/>
-      <c r="I104" s="33"/>
-      <c r="J104" s="33"/>
-      <c r="K104" s="33"/>
-      <c r="L104" s="33"/>
-      <c r="M104" s="25"/>
-    </row>
-    <row r="105" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="25"/>
-      <c r="B105" s="25"/>
-      <c r="C105" s="33"/>
-      <c r="D105" s="49"/>
-      <c r="E105" s="49"/>
-      <c r="F105" s="33"/>
-      <c r="G105" s="33"/>
-      <c r="H105" s="25"/>
-      <c r="I105" s="33"/>
-      <c r="J105" s="33"/>
-      <c r="K105" s="33"/>
-      <c r="L105" s="33"/>
-      <c r="M105" s="25"/>
-    </row>
-    <row r="106" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="25"/>
-      <c r="B106" s="25"/>
-      <c r="C106" s="33"/>
-      <c r="D106" s="49"/>
-      <c r="E106" s="49"/>
-      <c r="F106" s="33"/>
-      <c r="G106" s="33"/>
-      <c r="H106" s="25"/>
-      <c r="I106" s="33"/>
-      <c r="J106" s="33"/>
-      <c r="K106" s="33"/>
-      <c r="L106" s="33"/>
-      <c r="M106" s="25"/>
-    </row>
-    <row r="107" spans="1:13" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="25"/>
-      <c r="B107" s="25"/>
-      <c r="C107" s="33"/>
-      <c r="D107" s="49"/>
-      <c r="E107" s="49"/>
-      <c r="F107" s="33"/>
-      <c r="G107" s="33"/>
-      <c r="H107" s="25"/>
-      <c r="I107" s="33"/>
-      <c r="J107" s="33"/>
-      <c r="K107" s="33"/>
-      <c r="L107" s="33"/>
-      <c r="M107" s="25"/>
-    </row>
-    <row r="108" spans="1:13" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="25"/>
-      <c r="B108" s="25"/>
-      <c r="C108" s="33"/>
-      <c r="D108" s="49"/>
-      <c r="E108" s="49"/>
-      <c r="F108" s="33"/>
-      <c r="G108" s="33"/>
-      <c r="H108" s="25"/>
-      <c r="I108" s="33"/>
-      <c r="J108" s="33"/>
-      <c r="K108" s="33"/>
-      <c r="L108" s="33"/>
-      <c r="M108" s="25"/>
-    </row>
-    <row r="109" spans="1:13" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="25"/>
-      <c r="B109" s="25"/>
-      <c r="C109" s="33"/>
-      <c r="D109" s="49"/>
-      <c r="E109" s="49"/>
-      <c r="F109" s="33"/>
-      <c r="G109" s="33"/>
-      <c r="H109" s="25"/>
-      <c r="I109" s="33"/>
-      <c r="J109" s="33"/>
-      <c r="K109" s="33"/>
-      <c r="L109" s="33"/>
-      <c r="M109" s="25"/>
-    </row>
-    <row r="110" spans="1:13" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="25"/>
-      <c r="B110" s="25"/>
-      <c r="C110" s="33"/>
-      <c r="D110" s="49"/>
-      <c r="E110" s="49"/>
-      <c r="F110" s="33"/>
-      <c r="G110" s="33"/>
-      <c r="H110" s="25"/>
-      <c r="I110" s="33"/>
-      <c r="J110" s="33"/>
-      <c r="K110" s="33"/>
-      <c r="L110" s="33"/>
-      <c r="M110" s="25"/>
-    </row>
-    <row r="111" spans="1:13" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="27"/>
-      <c r="B111" s="27"/>
-      <c r="C111" s="34"/>
-      <c r="D111" s="50"/>
-      <c r="E111" s="50"/>
-      <c r="F111" s="34"/>
-      <c r="G111" s="34"/>
-      <c r="H111" s="27"/>
-      <c r="I111" s="34"/>
-      <c r="J111" s="34"/>
-      <c r="K111" s="34"/>
-      <c r="L111" s="34"/>
-      <c r="M111" s="27"/>
-    </row>
-    <row r="112" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="25"/>
+      <c r="G11" s="30" t="s">
+        <v>832</v>
+      </c>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="38"/>
+    </row>
+    <row r="12" spans="1:126" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+    </row>
+    <row r="13" spans="1:126" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+    </row>
+    <row r="14" spans="1:126" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+    </row>
+    <row r="15" spans="1:126" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+    </row>
+    <row r="16" spans="1:126" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+    </row>
+    <row r="17" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="34"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+    </row>
+    <row r="18" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+    </row>
+    <row r="19" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+    </row>
+    <row r="20" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+    </row>
+    <row r="21" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+    </row>
+    <row r="22" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+    </row>
+    <row r="23" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+    </row>
+    <row r="24" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="34"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
+    </row>
+    <row r="25" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+    </row>
+    <row r="26" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="34"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+    </row>
+    <row r="27" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="34"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+    </row>
+    <row r="28" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="34"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+    </row>
+    <row r="29" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="34"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
+    </row>
+    <row r="30" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="34"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+    </row>
+    <row r="31" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+    </row>
+    <row r="32" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="34"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+    </row>
+    <row r="33" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="34"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+    </row>
+    <row r="34" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="34"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+    </row>
+    <row r="35" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="34"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+    </row>
+    <row r="36" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="34"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+    </row>
+    <row r="37" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+    </row>
+    <row r="38" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="34"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="34"/>
+    </row>
+    <row r="39" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="34"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+    </row>
+    <row r="40" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="34"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="34"/>
+    </row>
+    <row r="41" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="34"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+    </row>
+    <row r="42" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="34"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+    </row>
+    <row r="43" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+    </row>
+    <row r="44" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="34"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+    </row>
+    <row r="45" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="34"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
+    </row>
+    <row r="46" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="34"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="34"/>
+    </row>
+    <row r="47" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="34"/>
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
+    </row>
+    <row r="48" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="34"/>
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+      <c r="J48" s="34"/>
+    </row>
+    <row r="49" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="34"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="34"/>
+    </row>
+    <row r="50" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="34"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="34"/>
+      <c r="I50" s="34"/>
+      <c r="J50" s="34"/>
+    </row>
+    <row r="51" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="34"/>
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+    </row>
+    <row r="52" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="34"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="34"/>
+      <c r="I52" s="34"/>
+      <c r="J52" s="34"/>
+    </row>
+    <row r="53" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="34"/>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="34"/>
+    </row>
+    <row r="54" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="34"/>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+    </row>
+    <row r="55" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+    </row>
+    <row r="56" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="34"/>
+      <c r="B56" s="34"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="34"/>
+      <c r="J56" s="34"/>
+    </row>
+    <row r="57" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="34"/>
+      <c r="B57" s="34"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="34"/>
+    </row>
+    <row r="58" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="34"/>
+      <c r="B58" s="34"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="34"/>
+      <c r="I58" s="34"/>
+      <c r="J58" s="34"/>
+    </row>
+    <row r="59" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="34"/>
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="34"/>
+      <c r="I59" s="34"/>
+      <c r="J59" s="34"/>
+    </row>
+    <row r="60" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="34"/>
+      <c r="B60" s="34"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
+      <c r="J60" s="34"/>
+    </row>
+    <row r="61" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="34"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="34"/>
+      <c r="I61" s="34"/>
+      <c r="J61" s="34"/>
+    </row>
+    <row r="62" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="34"/>
+      <c r="B62" s="34"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="34"/>
+    </row>
+    <row r="63" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="34"/>
+      <c r="B63" s="34"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="34"/>
+    </row>
+    <row r="64" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="34"/>
+      <c r="B64" s="34"/>
+      <c r="C64" s="34"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="34"/>
+      <c r="H64" s="34"/>
+      <c r="I64" s="34"/>
+      <c r="J64" s="34"/>
+    </row>
+    <row r="65" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="34"/>
+      <c r="B65" s="34"/>
+      <c r="C65" s="34"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="34"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
+      <c r="J65" s="34"/>
+    </row>
+    <row r="66" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="34"/>
+      <c r="B66" s="34"/>
+      <c r="C66" s="34"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="34"/>
+      <c r="H66" s="34"/>
+      <c r="I66" s="34"/>
+      <c r="J66" s="34"/>
+    </row>
+    <row r="67" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="34"/>
+      <c r="B67" s="34"/>
+      <c r="C67" s="34"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="34"/>
+      <c r="F67" s="34"/>
+      <c r="G67" s="34"/>
+      <c r="H67" s="34"/>
+      <c r="I67" s="34"/>
+      <c r="J67" s="34"/>
+    </row>
+    <row r="68" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="34"/>
+      <c r="B68" s="34"/>
+      <c r="C68" s="34"/>
+      <c r="D68" s="34"/>
+      <c r="E68" s="34"/>
+      <c r="F68" s="34"/>
+      <c r="G68" s="34"/>
+      <c r="H68" s="34"/>
+      <c r="I68" s="34"/>
+      <c r="J68" s="34"/>
+    </row>
+    <row r="69" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="34"/>
+      <c r="B69" s="34"/>
+      <c r="C69" s="34"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="34"/>
+      <c r="F69" s="34"/>
+      <c r="G69" s="34"/>
+      <c r="H69" s="34"/>
+      <c r="I69" s="34"/>
+      <c r="J69" s="34"/>
+    </row>
+    <row r="70" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="34"/>
+      <c r="B70" s="34"/>
+      <c r="C70" s="34"/>
+      <c r="D70" s="34"/>
+      <c r="E70" s="34"/>
+      <c r="F70" s="34"/>
+      <c r="G70" s="34"/>
+      <c r="H70" s="34"/>
+      <c r="I70" s="34"/>
+      <c r="J70" s="34"/>
+    </row>
+    <row r="71" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="34"/>
+      <c r="B71" s="34"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="34"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="34"/>
+      <c r="J71" s="34"/>
+    </row>
+    <row r="72" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="34"/>
+      <c r="B72" s="34"/>
+      <c r="C72" s="34"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="34"/>
+      <c r="H72" s="34"/>
+      <c r="I72" s="34"/>
+      <c r="J72" s="34"/>
+    </row>
+    <row r="73" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="34"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="34"/>
+      <c r="F73" s="34"/>
+      <c r="G73" s="34"/>
+      <c r="H73" s="34"/>
+      <c r="I73" s="34"/>
+      <c r="J73" s="34"/>
+    </row>
+    <row r="74" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="34"/>
+      <c r="B74" s="34"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="34"/>
+      <c r="F74" s="34"/>
+      <c r="G74" s="34"/>
+      <c r="H74" s="34"/>
+      <c r="I74" s="34"/>
+      <c r="J74" s="34"/>
+    </row>
+    <row r="75" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="34"/>
+      <c r="B75" s="34"/>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="34"/>
+      <c r="G75" s="34"/>
+      <c r="H75" s="34"/>
+      <c r="I75" s="34"/>
+      <c r="J75" s="34"/>
+    </row>
+    <row r="76" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="34"/>
+      <c r="B76" s="34"/>
+      <c r="C76" s="34"/>
+      <c r="D76" s="34"/>
+      <c r="E76" s="34"/>
+      <c r="F76" s="34"/>
+      <c r="G76" s="34"/>
+      <c r="H76" s="34"/>
+      <c r="I76" s="34"/>
+      <c r="J76" s="34"/>
+    </row>
+    <row r="77" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="34"/>
+      <c r="B77" s="34"/>
+      <c r="C77" s="34"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="34"/>
+      <c r="H77" s="34"/>
+      <c r="I77" s="34"/>
+      <c r="J77" s="34"/>
+    </row>
+    <row r="78" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="34"/>
+      <c r="B78" s="34"/>
+      <c r="C78" s="34"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="34"/>
+      <c r="F78" s="34"/>
+      <c r="G78" s="34"/>
+      <c r="H78" s="34"/>
+      <c r="I78" s="34"/>
+      <c r="J78" s="34"/>
+    </row>
+    <row r="79" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="34"/>
+      <c r="B79" s="34"/>
+      <c r="C79" s="34"/>
+      <c r="D79" s="34"/>
+      <c r="E79" s="34"/>
+      <c r="F79" s="34"/>
+      <c r="G79" s="34"/>
+      <c r="H79" s="34"/>
+      <c r="I79" s="34"/>
+      <c r="J79" s="34"/>
+    </row>
+    <row r="80" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="34"/>
+      <c r="B80" s="34"/>
+      <c r="C80" s="34"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="34"/>
+      <c r="F80" s="34"/>
+      <c r="G80" s="34"/>
+      <c r="H80" s="34"/>
+      <c r="I80" s="34"/>
+      <c r="J80" s="34"/>
+    </row>
+    <row r="81" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="22"/>
+      <c r="B81" s="35"/>
+      <c r="C81" s="35"/>
+      <c r="D81" s="35"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="35"/>
+      <c r="G81" s="35"/>
+      <c r="H81" s="35"/>
+      <c r="I81" s="35"/>
+      <c r="J81" s="35"/>
+    </row>
+    <row r="82" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="22"/>
+      <c r="B82" s="35"/>
+      <c r="C82" s="35"/>
+      <c r="D82" s="35"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="35"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="35"/>
+      <c r="I82" s="35"/>
+      <c r="J82" s="35"/>
+    </row>
+    <row r="83" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="22"/>
+      <c r="B83" s="35"/>
+      <c r="C83" s="35"/>
+      <c r="D83" s="35"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="35"/>
+      <c r="G83" s="35"/>
+      <c r="H83" s="35"/>
+      <c r="I83" s="35"/>
+      <c r="J83" s="35"/>
+    </row>
+    <row r="84" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="22"/>
+      <c r="B84" s="35"/>
+      <c r="C84" s="35"/>
+      <c r="D84" s="35"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="35"/>
+      <c r="G84" s="35"/>
+      <c r="H84" s="35"/>
+      <c r="I84" s="35"/>
+      <c r="J84" s="35"/>
+    </row>
+    <row r="85" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="22"/>
+      <c r="B85" s="35"/>
+      <c r="C85" s="35"/>
+      <c r="D85" s="35"/>
+      <c r="E85" s="22"/>
+      <c r="F85" s="35"/>
+      <c r="G85" s="35"/>
+      <c r="H85" s="35"/>
+      <c r="I85" s="35"/>
+      <c r="J85" s="35"/>
+    </row>
+    <row r="86" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="22"/>
+      <c r="B86" s="35"/>
+      <c r="C86" s="35"/>
+      <c r="D86" s="35"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="35"/>
+      <c r="G86" s="35"/>
+      <c r="H86" s="35"/>
+      <c r="I86" s="35"/>
+      <c r="J86" s="35"/>
+    </row>
+    <row r="87" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="22"/>
+      <c r="B87" s="35"/>
+      <c r="C87" s="35"/>
+      <c r="D87" s="35"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="35"/>
+      <c r="G87" s="35"/>
+      <c r="H87" s="35"/>
+      <c r="I87" s="35"/>
+      <c r="J87" s="35"/>
+    </row>
+    <row r="88" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="22"/>
+      <c r="B88" s="35"/>
+      <c r="C88" s="35"/>
+      <c r="D88" s="35"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="35"/>
+      <c r="G88" s="35"/>
+      <c r="H88" s="35"/>
+      <c r="I88" s="35"/>
+      <c r="J88" s="35"/>
+    </row>
+    <row r="89" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="22"/>
+      <c r="B89" s="35"/>
+      <c r="C89" s="35"/>
+      <c r="D89" s="35"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="35"/>
+      <c r="G89" s="35"/>
+      <c r="H89" s="35"/>
+      <c r="I89" s="35"/>
+      <c r="J89" s="35"/>
+    </row>
+    <row r="90" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="22"/>
+      <c r="B90" s="35"/>
+      <c r="C90" s="35"/>
+      <c r="D90" s="35"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="35"/>
+      <c r="G90" s="35"/>
+      <c r="H90" s="35"/>
+      <c r="I90" s="35"/>
+      <c r="J90" s="35"/>
+    </row>
+    <row r="91" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="22"/>
+      <c r="B91" s="35"/>
+      <c r="C91" s="35"/>
+      <c r="D91" s="35"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="35"/>
+      <c r="H91" s="35"/>
+      <c r="I91" s="35"/>
+      <c r="J91" s="35"/>
+    </row>
+    <row r="92" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="22"/>
+      <c r="B92" s="35"/>
+      <c r="C92" s="35"/>
+      <c r="D92" s="35"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="35"/>
+      <c r="G92" s="35"/>
+      <c r="H92" s="35"/>
+      <c r="I92" s="35"/>
+      <c r="J92" s="35"/>
+    </row>
+    <row r="93" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="22"/>
+      <c r="B93" s="35"/>
+      <c r="C93" s="35"/>
+      <c r="D93" s="35"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="35"/>
+      <c r="G93" s="35"/>
+      <c r="H93" s="35"/>
+      <c r="I93" s="35"/>
+      <c r="J93" s="35"/>
+    </row>
+    <row r="94" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="22"/>
+      <c r="B94" s="35"/>
+      <c r="C94" s="35"/>
+      <c r="D94" s="35"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="35"/>
+      <c r="G94" s="35"/>
+      <c r="H94" s="35"/>
+      <c r="I94" s="35"/>
+      <c r="J94" s="35"/>
+    </row>
+    <row r="95" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="22"/>
+      <c r="B95" s="35"/>
+      <c r="C95" s="35"/>
+      <c r="D95" s="35"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="35"/>
+      <c r="G95" s="35"/>
+      <c r="H95" s="35"/>
+      <c r="I95" s="35"/>
+      <c r="J95" s="35"/>
+    </row>
+    <row r="96" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="22"/>
+      <c r="B96" s="35"/>
+      <c r="C96" s="35"/>
+      <c r="D96" s="35"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="35"/>
+      <c r="G96" s="35"/>
+      <c r="H96" s="35"/>
+      <c r="I96" s="35"/>
+      <c r="J96" s="35"/>
+    </row>
+    <row r="97" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="22"/>
+      <c r="B97" s="35"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="35"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="35"/>
+      <c r="G97" s="35"/>
+      <c r="H97" s="35"/>
+      <c r="I97" s="35"/>
+      <c r="J97" s="35"/>
+    </row>
+    <row r="98" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="22"/>
+      <c r="B98" s="35"/>
+      <c r="C98" s="35"/>
+      <c r="D98" s="35"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="35"/>
+      <c r="G98" s="35"/>
+      <c r="H98" s="35"/>
+      <c r="I98" s="35"/>
+      <c r="J98" s="35"/>
+    </row>
+    <row r="99" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="22"/>
+      <c r="B99" s="35"/>
+      <c r="C99" s="35"/>
+      <c r="D99" s="35"/>
+      <c r="E99" s="22"/>
+      <c r="F99" s="35"/>
+      <c r="G99" s="35"/>
+      <c r="H99" s="35"/>
+      <c r="I99" s="35"/>
+      <c r="J99" s="35"/>
+    </row>
+    <row r="100" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="22"/>
+      <c r="B100" s="35"/>
+      <c r="C100" s="35"/>
+      <c r="D100" s="35"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="35"/>
+      <c r="G100" s="35"/>
+      <c r="H100" s="35"/>
+      <c r="I100" s="35"/>
+      <c r="J100" s="35"/>
+    </row>
+    <row r="101" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="22"/>
+      <c r="B101" s="35"/>
+      <c r="C101" s="35"/>
+      <c r="D101" s="35"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="35"/>
+      <c r="G101" s="35"/>
+      <c r="H101" s="35"/>
+      <c r="I101" s="35"/>
+      <c r="J101" s="35"/>
+    </row>
+    <row r="102" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="22"/>
+      <c r="B102" s="35"/>
+      <c r="C102" s="35"/>
+      <c r="D102" s="35"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="35"/>
+      <c r="G102" s="35"/>
+      <c r="H102" s="35"/>
+      <c r="I102" s="35"/>
+      <c r="J102" s="35"/>
+    </row>
+    <row r="103" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="22"/>
+      <c r="B103" s="35"/>
+      <c r="C103" s="35"/>
+      <c r="D103" s="35"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="35"/>
+      <c r="G103" s="35"/>
+      <c r="H103" s="35"/>
+      <c r="I103" s="35"/>
+      <c r="J103" s="35"/>
+    </row>
+    <row r="104" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="22"/>
+      <c r="B104" s="35"/>
+      <c r="C104" s="35"/>
+      <c r="D104" s="35"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="35"/>
+      <c r="G104" s="35"/>
+      <c r="H104" s="35"/>
+      <c r="I104" s="35"/>
+      <c r="J104" s="35"/>
+    </row>
+    <row r="105" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="22"/>
+      <c r="B105" s="35"/>
+      <c r="C105" s="35"/>
+      <c r="D105" s="35"/>
+      <c r="E105" s="22"/>
+      <c r="F105" s="35"/>
+      <c r="G105" s="35"/>
+      <c r="H105" s="35"/>
+      <c r="I105" s="35"/>
+      <c r="J105" s="35"/>
+    </row>
+    <row r="106" spans="1:10" s="23" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="22"/>
+      <c r="B106" s="35"/>
+      <c r="C106" s="35"/>
+      <c r="D106" s="35"/>
+      <c r="E106" s="22"/>
+      <c r="F106" s="35"/>
+      <c r="G106" s="35"/>
+      <c r="H106" s="35"/>
+      <c r="I106" s="35"/>
+      <c r="J106" s="35"/>
+    </row>
+    <row r="107" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="22"/>
+      <c r="B107" s="35"/>
+      <c r="C107" s="35"/>
+      <c r="D107" s="35"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="35"/>
+      <c r="G107" s="35"/>
+      <c r="H107" s="35"/>
+      <c r="I107" s="35"/>
+      <c r="J107" s="35"/>
+    </row>
+    <row r="108" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="22"/>
+      <c r="B108" s="35"/>
+      <c r="C108" s="35"/>
+      <c r="D108" s="35"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="35"/>
+      <c r="G108" s="35"/>
+      <c r="H108" s="35"/>
+      <c r="I108" s="35"/>
+      <c r="J108" s="35"/>
+    </row>
+    <row r="109" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="22"/>
+      <c r="B109" s="35"/>
+      <c r="C109" s="35"/>
+      <c r="D109" s="35"/>
+      <c r="E109" s="22"/>
+      <c r="F109" s="35"/>
+      <c r="G109" s="35"/>
+      <c r="H109" s="35"/>
+      <c r="I109" s="35"/>
+      <c r="J109" s="35"/>
+    </row>
+    <row r="110" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="22"/>
+      <c r="B110" s="35"/>
+      <c r="C110" s="35"/>
+      <c r="D110" s="35"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="35"/>
+      <c r="G110" s="35"/>
+      <c r="H110" s="35"/>
+      <c r="I110" s="35"/>
+      <c r="J110" s="35"/>
+    </row>
+    <row r="111" spans="1:10" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="11"/>
+      <c r="B111" s="11"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="11"/>
+      <c r="I111" s="11"/>
+      <c r="J111" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="122">
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="D92:E92"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D93:E93"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="D109:E109"/>
-    <mergeCell ref="D110:E110"/>
-    <mergeCell ref="D111:E111"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="D94:E94"/>
-    <mergeCell ref="D95:E95"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="D97:E97"/>
-    <mergeCell ref="D98:E98"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="D100:E100"/>
-    <mergeCell ref="D101:E101"/>
-    <mergeCell ref="D102:E102"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="E1:H3"/>
+  <mergeCells count="16">
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="H8:J8"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="D10:E11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B1:E3"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
-  <conditionalFormatting sqref="J12:K111">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(J12))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -6009,28 +5548,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q148"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="6.28515625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="8.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="4.28515625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.5703125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="10.81640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="7.54296875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.26953125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="6.26953125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="5.26953125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.453125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="4.81640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="4.26953125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="15.54296875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.54296875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12.54296875" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -6038,10 +5577,10 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="E1" s="3">
         <v>1</v>
@@ -6065,10 +5604,10 @@
         <v>0.01</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>211</v>
@@ -6078,7 +5617,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -6086,10 +5625,10 @@
         <v>98</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E2" s="3">
         <v>2</v>
@@ -6113,10 +5652,10 @@
         <v>0.02</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>213</v>
@@ -6126,7 +5665,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -6134,10 +5673,10 @@
         <v>97</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E3" s="3">
         <v>3</v>
@@ -6161,10 +5700,10 @@
         <v>0.03</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>215</v>
@@ -6174,7 +5713,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -6182,10 +5721,10 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="E4" s="3">
         <v>4</v>
@@ -6209,10 +5748,10 @@
         <v>0.04</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>217</v>
@@ -6220,7 +5759,7 @@
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -6228,10 +5767,10 @@
         <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E5" s="3">
         <v>5</v>
@@ -6255,10 +5794,10 @@
         <v>0.05</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>219</v>
@@ -6268,7 +5807,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -6276,10 +5815,10 @@
         <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E6" s="3">
         <v>6</v>
@@ -6303,20 +5842,20 @@
         <v>0.06</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="N6" s="8" t="s">
         <v>221</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="9" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -6324,10 +5863,10 @@
         <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E7" s="3">
         <v>7</v>
@@ -6351,20 +5890,20 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>223</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -6372,10 +5911,10 @@
         <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E8" s="3">
         <v>8</v>
@@ -6399,10 +5938,10 @@
         <v>0.08</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>225</v>
@@ -6410,7 +5949,7 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -6418,10 +5957,10 @@
         <v>91</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E9" s="3">
         <v>9</v>
@@ -6445,10 +5984,10 @@
         <v>0.09</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>227</v>
@@ -6460,7 +5999,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -6468,10 +6007,10 @@
         <v>90</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E10" s="3">
         <v>10</v>
@@ -6495,22 +6034,22 @@
         <v>0.1</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>229</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -6518,10 +6057,10 @@
         <v>89</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E11" s="3">
         <v>11</v>
@@ -6545,22 +6084,22 @@
         <v>0.11</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>231</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -6568,10 +6107,10 @@
         <v>88</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="E12" s="3">
         <v>12</v>
@@ -6595,22 +6134,22 @@
         <v>0.12</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>233</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -6618,10 +6157,10 @@
         <v>87</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E13" s="3">
         <v>13</v>
@@ -6645,16 +6184,16 @@
         <v>0.13</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="N13" s="8" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
@@ -6662,10 +6201,10 @@
         <v>86</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E14" s="3">
         <v>14</v>
@@ -6689,16 +6228,16 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="N14" s="8" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -6706,10 +6245,10 @@
         <v>85</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E15" s="3">
         <v>15</v>
@@ -6733,16 +6272,16 @@
         <v>0.15</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
@@ -6750,10 +6289,10 @@
         <v>84</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="E16" s="3">
         <v>16</v>
@@ -6777,16 +6316,16 @@
         <v>0.16</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="N16" s="8" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
@@ -6794,10 +6333,10 @@
         <v>83</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="E17" s="3">
         <v>17</v>
@@ -6821,16 +6360,16 @@
         <v>0.17</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="N17" s="8" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
@@ -6838,10 +6377,10 @@
         <v>82</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="E18" s="3">
         <v>18</v>
@@ -6865,16 +6404,16 @@
         <v>0.18</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N18" s="8" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -6882,10 +6421,10 @@
         <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="E19" s="3">
         <v>19</v>
@@ -6909,16 +6448,16 @@
         <v>0.19</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="N19" s="8" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -6926,10 +6465,10 @@
         <v>80</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E20" s="3">
         <v>20</v>
@@ -6953,16 +6492,16 @@
         <v>0.2</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="N20" s="8" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>30</v>
       </c>
@@ -6970,10 +6509,10 @@
         <v>79</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E21" s="3">
         <v>21</v>
@@ -6997,16 +6536,16 @@
         <v>0.21</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="N21" s="8" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
@@ -7014,10 +6553,10 @@
         <v>78</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E22" s="3">
         <v>22</v>
@@ -7041,16 +6580,16 @@
         <v>0.22</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="N22" s="8" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
@@ -7058,10 +6597,10 @@
         <v>77</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="E23" s="3">
         <v>23</v>
@@ -7085,16 +6624,16 @@
         <v>0.23</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="N23" s="8" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>33</v>
       </c>
@@ -7102,10 +6641,10 @@
         <v>76</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E24" s="3">
         <v>24</v>
@@ -7129,16 +6668,16 @@
         <v>0.24</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="N24" s="8" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>34</v>
       </c>
@@ -7146,10 +6685,10 @@
         <v>75</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E25" s="3">
         <v>25</v>
@@ -7173,16 +6712,16 @@
         <v>0.25</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="N25" s="8" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>35</v>
       </c>
@@ -7190,10 +6729,10 @@
         <v>74</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="E26" s="3">
         <v>26</v>
@@ -7217,16 +6756,16 @@
         <v>0.26</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="N26" s="8" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>36</v>
       </c>
@@ -7234,10 +6773,10 @@
         <v>73</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="E27" s="3">
         <v>27</v>
@@ -7261,16 +6800,16 @@
         <v>0.27</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="N27" s="8" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
@@ -7278,10 +6817,10 @@
         <v>72</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="E28" s="3">
         <v>28</v>
@@ -7305,16 +6844,16 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="N28" s="8" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>38</v>
       </c>
@@ -7322,10 +6861,10 @@
         <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="E29" s="3">
         <v>29</v>
@@ -7349,16 +6888,16 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="N29" s="8" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>39</v>
       </c>
@@ -7366,10 +6905,10 @@
         <v>70</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E30" s="3">
         <v>30</v>
@@ -7393,16 +6932,16 @@
         <v>0.3</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="N30" s="8" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
@@ -7410,10 +6949,10 @@
         <v>69</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E31" s="3">
         <v>31</v>
@@ -7437,16 +6976,16 @@
         <v>0.31</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="N31" s="8" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>41</v>
       </c>
@@ -7454,10 +6993,10 @@
         <v>68</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="E32" s="3">
         <v>32</v>
@@ -7481,16 +7020,16 @@
         <v>0.32</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="N32" s="8" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>42</v>
       </c>
@@ -7498,10 +7037,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E33" s="3">
         <v>33</v>
@@ -7525,16 +7064,16 @@
         <v>0.33</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="N33" s="8" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>43</v>
       </c>
@@ -7542,10 +7081,10 @@
         <v>66</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E34" s="3">
         <v>34</v>
@@ -7569,16 +7108,16 @@
         <v>0.34</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="N34" s="8" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>44</v>
       </c>
@@ -7586,10 +7125,10 @@
         <v>65</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E35" s="3">
         <v>35</v>
@@ -7613,16 +7152,16 @@
         <v>0.35</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="N35" s="8" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>45</v>
       </c>
@@ -7630,10 +7169,10 @@
         <v>64</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E36" s="3">
         <v>36</v>
@@ -7657,16 +7196,16 @@
         <v>0.36</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="N36" s="8" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>46</v>
       </c>
@@ -7674,10 +7213,10 @@
         <v>63</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E37" s="3">
         <v>37</v>
@@ -7701,16 +7240,16 @@
         <v>0.37</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N37" s="8" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>47</v>
       </c>
@@ -7718,10 +7257,10 @@
         <v>62</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E38" s="3">
         <v>38</v>
@@ -7745,16 +7284,16 @@
         <v>0.38</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="N38" s="8" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>48</v>
       </c>
@@ -7762,10 +7301,10 @@
         <v>61</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E39" s="3">
         <v>39</v>
@@ -7789,16 +7328,16 @@
         <v>0.39</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N39" s="8" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>49</v>
       </c>
@@ -7806,10 +7345,10 @@
         <v>60</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E40" s="3">
         <v>40</v>
@@ -7833,16 +7372,16 @@
         <v>0.4</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="N40" s="8" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>50</v>
       </c>
@@ -7850,10 +7389,10 @@
         <v>59</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="E41" s="3">
         <v>41</v>
@@ -7877,16 +7416,16 @@
         <v>0.41</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="N41" s="8" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>51</v>
       </c>
@@ -7894,10 +7433,10 @@
         <v>58</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="E42" s="3">
         <v>42</v>
@@ -7921,16 +7460,16 @@
         <v>0.42</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="N42" s="8" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>52</v>
       </c>
@@ -7938,10 +7477,10 @@
         <v>57</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E43" s="3">
         <v>43</v>
@@ -7965,16 +7504,16 @@
         <v>0.43</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="N43" s="8" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>53</v>
       </c>
@@ -7982,10 +7521,10 @@
         <v>56</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E44" s="3">
         <v>44</v>
@@ -8009,16 +7548,16 @@
         <v>0.44</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="N44" s="8" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>54</v>
       </c>
@@ -8026,10 +7565,10 @@
         <v>55</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E45" s="3">
         <v>45</v>
@@ -8053,16 +7592,16 @@
         <v>0.45</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="N45" s="8" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>55</v>
       </c>
@@ -8070,10 +7609,10 @@
         <v>54</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E46" s="3">
         <v>46</v>
@@ -8097,16 +7636,16 @@
         <v>0.46</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="N46" s="8" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>56</v>
       </c>
@@ -8114,10 +7653,10 @@
         <v>53</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E47" s="3">
         <v>47</v>
@@ -8141,16 +7680,16 @@
         <v>0.47</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N47" s="8" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>57</v>
       </c>
@@ -8158,10 +7697,10 @@
         <v>52</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E48" s="3">
         <v>48</v>
@@ -8185,16 +7724,16 @@
         <v>0.48</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="N48" s="8" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>58</v>
       </c>
@@ -8202,10 +7741,10 @@
         <v>51</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E49" s="3">
         <v>49</v>
@@ -8229,16 +7768,16 @@
         <v>0.49</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="N49" s="8" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>59</v>
       </c>
@@ -8246,10 +7785,10 @@
         <v>50</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="E50" s="3">
         <v>50</v>
@@ -8273,16 +7812,16 @@
         <v>0.5</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="N50" s="8" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>60</v>
       </c>
@@ -8290,10 +7829,10 @@
         <v>49</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E51" s="3">
         <v>51</v>
@@ -8317,16 +7856,16 @@
         <v>0.51</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="N51" s="8" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>61</v>
       </c>
@@ -8334,10 +7873,10 @@
         <v>48</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="E52" s="3">
         <v>52</v>
@@ -8361,16 +7900,16 @@
         <v>0.52</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="N52" s="8" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>62</v>
       </c>
@@ -8378,10 +7917,10 @@
         <v>47</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E53" s="3">
         <v>53</v>
@@ -8405,16 +7944,16 @@
         <v>0.53</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N53" s="8" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>63</v>
       </c>
@@ -8422,10 +7961,10 @@
         <v>46</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E54" s="3">
         <v>54</v>
@@ -8449,16 +7988,16 @@
         <v>0.54</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="N54" s="8" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>64</v>
       </c>
@@ -8466,10 +8005,10 @@
         <v>45</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E55" s="3">
         <v>55</v>
@@ -8493,16 +8032,16 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="N55" s="8" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>65</v>
       </c>
@@ -8510,10 +8049,10 @@
         <v>44</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="E56" s="3">
         <v>56</v>
@@ -8537,16 +8076,16 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="N56" s="8" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>66</v>
       </c>
@@ -8554,10 +8093,10 @@
         <v>43</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E57" s="3">
         <v>57</v>
@@ -8581,16 +8120,16 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="N57" s="8" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>67</v>
       </c>
@@ -8598,10 +8137,10 @@
         <v>42</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="E58" s="3">
         <v>58</v>
@@ -8625,16 +8164,16 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="N58" s="8" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>68</v>
       </c>
@@ -8642,10 +8181,10 @@
         <v>41</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E59" s="3">
         <v>59</v>
@@ -8669,16 +8208,16 @@
         <v>0.59</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="N59" s="8" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>69</v>
       </c>
@@ -8686,10 +8225,10 @@
         <v>40</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E60" s="3">
         <v>60</v>
@@ -8713,16 +8252,16 @@
         <v>0.6</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N60" s="8" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>70</v>
       </c>
@@ -8730,10 +8269,10 @@
         <v>39</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E61" s="3">
         <v>61</v>
@@ -8757,16 +8296,16 @@
         <v>0.61</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="N61" s="8" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>71</v>
       </c>
@@ -8774,10 +8313,10 @@
         <v>38</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="E62" s="3">
         <v>62</v>
@@ -8801,16 +8340,16 @@
         <v>0.62</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="N62" s="8" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>72</v>
       </c>
@@ -8818,10 +8357,10 @@
         <v>37</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E63" s="3">
         <v>63</v>
@@ -8845,16 +8384,16 @@
         <v>0.63</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="N63" s="8" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>73</v>
       </c>
@@ -8862,10 +8401,10 @@
         <v>36</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="E64" s="3">
         <v>64</v>
@@ -8889,16 +8428,16 @@
         <v>0.64</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="N64" s="8" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>74</v>
       </c>
@@ -8906,10 +8445,10 @@
         <v>35</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E65" s="3">
         <v>65</v>
@@ -8933,16 +8472,16 @@
         <v>0.65</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N65" s="8" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>75</v>
       </c>
@@ -8950,10 +8489,10 @@
         <v>34</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="E66" s="3">
         <v>66</v>
@@ -8977,16 +8516,16 @@
         <v>0.66</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N66" s="8" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>76</v>
       </c>
@@ -8994,10 +8533,10 @@
         <v>33</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="E67" s="3">
         <v>67</v>
@@ -9021,16 +8560,16 @@
         <v>0.67</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N67" s="8" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>77</v>
       </c>
@@ -9038,10 +8577,10 @@
         <v>32</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="E68" s="3">
         <v>68</v>
@@ -9065,16 +8604,16 @@
         <v>0.68</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N68" s="8" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>78</v>
       </c>
@@ -9082,10 +8621,10 @@
         <v>31</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="E69" s="3">
         <v>69</v>
@@ -9109,16 +8648,16 @@
         <v>0.69</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N69" s="8" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>79</v>
       </c>
@@ -9126,10 +8665,10 @@
         <v>30</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="E70" s="3">
         <v>70</v>
@@ -9153,16 +8692,16 @@
         <v>0.7</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N70" s="8" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>80</v>
       </c>
@@ -9170,10 +8709,10 @@
         <v>29</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="E71" s="3">
         <v>71</v>
@@ -9197,16 +8736,16 @@
         <v>0.71</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N71" s="8" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>81</v>
       </c>
@@ -9214,10 +8753,10 @@
         <v>28</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E72" s="3">
         <v>72</v>
@@ -9241,16 +8780,16 @@
         <v>0.72</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N72" s="8" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>82</v>
       </c>
@@ -9258,10 +8797,10 @@
         <v>27</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="E73" s="3">
         <v>73</v>
@@ -9285,16 +8824,16 @@
         <v>0.73</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N73" s="8" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>83</v>
       </c>
@@ -9302,10 +8841,10 @@
         <v>26</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E74" s="3">
         <v>74</v>
@@ -9329,16 +8868,16 @@
         <v>0.74</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="N74" s="8" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>84</v>
       </c>
@@ -9346,10 +8885,10 @@
         <v>25</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="E75" s="3">
         <v>75</v>
@@ -9373,16 +8912,16 @@
         <v>0.75</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="N75" s="8" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>85</v>
       </c>
@@ -9390,10 +8929,10 @@
         <v>24</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E76" s="3">
         <v>76</v>
@@ -9417,16 +8956,16 @@
         <v>0.76</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="N76" s="8" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>86</v>
       </c>
@@ -9434,10 +8973,10 @@
         <v>23</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="E77" s="3">
         <v>77</v>
@@ -9461,16 +9000,16 @@
         <v>0.77</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="N77" s="8" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>87</v>
       </c>
@@ -9478,10 +9017,10 @@
         <v>22</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="E78" s="3">
         <v>78</v>
@@ -9505,16 +9044,16 @@
         <v>0.78</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="N78" s="8" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>88</v>
       </c>
@@ -9522,10 +9061,10 @@
         <v>21</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="E79" s="3">
         <v>79</v>
@@ -9549,16 +9088,16 @@
         <v>0.79</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="N79" s="8" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>89</v>
       </c>
@@ -9566,10 +9105,10 @@
         <v>20</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="E80" s="3">
         <v>80</v>
@@ -9593,16 +9132,16 @@
         <v>0.8</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="N80" s="8" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>90</v>
       </c>
@@ -9610,10 +9149,10 @@
         <v>19</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="E81" s="3">
         <v>81</v>
@@ -9637,16 +9176,16 @@
         <v>0.81</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="N81" s="8" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>91</v>
       </c>
@@ -9654,10 +9193,10 @@
         <v>18</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="E82" s="3">
         <v>82</v>
@@ -9681,16 +9220,16 @@
         <v>0.82</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="N82" s="8" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>92</v>
       </c>
@@ -9698,10 +9237,10 @@
         <v>17</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="E83" s="3">
         <v>83</v>
@@ -9725,16 +9264,16 @@
         <v>0.83</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="N83" s="8" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>93</v>
       </c>
@@ -9742,10 +9281,10 @@
         <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="E84" s="3">
         <v>84</v>
@@ -9769,16 +9308,16 @@
         <v>0.84</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="N84" s="8" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>94</v>
       </c>
@@ -9786,10 +9325,10 @@
         <v>15</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="E85" s="3">
         <v>85</v>
@@ -9813,16 +9352,16 @@
         <v>0.85</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="N85" s="8" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>95</v>
       </c>
@@ -9830,10 +9369,10 @@
         <v>14</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="E86" s="3">
         <v>86</v>
@@ -9857,16 +9396,16 @@
         <v>0.86</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="N86" s="8" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>96</v>
       </c>
@@ -9874,10 +9413,10 @@
         <v>13</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="E87" s="3">
         <v>87</v>
@@ -9901,16 +9440,16 @@
         <v>0.87</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="N87" s="8" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>97</v>
       </c>
@@ -9918,10 +9457,10 @@
         <v>12</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="E88" s="3">
         <v>88</v>
@@ -9945,16 +9484,16 @@
         <v>0.88</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="N88" s="8" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>98</v>
       </c>
@@ -9962,10 +9501,10 @@
         <v>11</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="E89" s="3">
         <v>89</v>
@@ -9989,16 +9528,16 @@
         <v>0.89</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="N89" s="8" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>99</v>
       </c>
@@ -10006,10 +9545,10 @@
         <v>10</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="E90" s="3">
         <v>90</v>
@@ -10033,16 +9572,16 @@
         <v>0.9</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="N90" s="8" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>100</v>
       </c>
@@ -10050,10 +9589,10 @@
         <v>9</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="E91" s="3">
         <v>91</v>
@@ -10077,16 +9616,16 @@
         <v>0.91</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="N91" s="8" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>101</v>
       </c>
@@ -10094,10 +9633,10 @@
         <v>8</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="E92" s="3">
         <v>92</v>
@@ -10121,16 +9660,16 @@
         <v>0.92</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="N92" s="8" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>102</v>
       </c>
@@ -10138,10 +9677,10 @@
         <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="E93" s="3">
         <v>93</v>
@@ -10165,16 +9704,16 @@
         <v>0.93</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="N93" s="8" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>103</v>
       </c>
@@ -10182,10 +9721,10 @@
         <v>6</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="E94" s="3">
         <v>94</v>
@@ -10209,16 +9748,16 @@
         <v>0.94</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="N94" s="8" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>104</v>
       </c>
@@ -10226,10 +9765,10 @@
         <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="E95" s="3">
         <v>95</v>
@@ -10253,16 +9792,16 @@
         <v>0.95</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="N95" s="8" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>105</v>
       </c>
@@ -10270,10 +9809,10 @@
         <v>4</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="E96" s="3">
         <v>96</v>
@@ -10297,16 +9836,16 @@
         <v>0.96</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="N96" s="8" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>106</v>
       </c>
@@ -10314,10 +9853,10 @@
         <v>3</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="E97" s="3">
         <v>97</v>
@@ -10341,16 +9880,16 @@
         <v>0.97</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="N97" s="8" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>107</v>
       </c>
@@ -10358,10 +9897,10 @@
         <v>2</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="E98" s="3">
         <v>98</v>
@@ -10385,16 +9924,16 @@
         <v>0.98</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="N98" s="8" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>108</v>
       </c>
@@ -10402,10 +9941,10 @@
         <v>1</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E99" s="3">
         <v>99</v>
@@ -10429,16 +9968,16 @@
         <v>0.99</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="N99" s="8" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>109</v>
       </c>
@@ -10446,10 +9985,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E100" s="3">
         <v>100</v>
@@ -10473,169 +10012,169 @@
         <v>1</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="N100" s="8" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C101" s="2"/>
       <c r="G101" s="2"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C102" s="2"/>
       <c r="G102" s="2"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C103" s="2"/>
       <c r="G103" s="2"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C104" s="2"/>
       <c r="G104" s="2"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C105" s="2"/>
       <c r="G105" s="2"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C106" s="2"/>
       <c r="G106" s="2"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C107" s="2"/>
       <c r="G107" s="2"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C108" s="2"/>
       <c r="G108" s="2"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C109" s="2"/>
       <c r="G109" s="2"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C110" s="2"/>
       <c r="G110" s="2"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C111" s="2"/>
       <c r="G111" s="2"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C112" s="2"/>
       <c r="G112" s="2"/>
     </row>
-    <row r="113" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D113" s="3"/>
     </row>
-    <row r="114" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D114" s="3"/>
     </row>
-    <row r="115" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D115" s="3"/>
     </row>
-    <row r="116" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D116" s="3"/>
     </row>
-    <row r="117" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D117" s="3"/>
     </row>
-    <row r="118" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D118" s="3"/>
     </row>
-    <row r="119" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D119" s="3"/>
     </row>
-    <row r="120" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D120" s="3"/>
     </row>
-    <row r="121" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D121" s="3"/>
     </row>
-    <row r="122" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D122" s="3"/>
     </row>
-    <row r="123" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D123" s="3"/>
     </row>
-    <row r="124" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D124" s="3"/>
     </row>
-    <row r="125" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D125" s="3"/>
     </row>
-    <row r="126" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D126" s="3"/>
     </row>
-    <row r="127" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D127" s="3"/>
     </row>
-    <row r="128" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D128" s="3"/>
     </row>
-    <row r="129" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D129" s="3"/>
     </row>
-    <row r="130" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D130" s="3"/>
     </row>
-    <row r="131" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D131" s="3"/>
     </row>
-    <row r="132" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D132" s="3"/>
     </row>
-    <row r="133" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D133" s="3"/>
     </row>
-    <row r="134" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D134" s="3"/>
     </row>
-    <row r="135" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D135" s="3"/>
     </row>
-    <row r="136" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D136" s="3"/>
     </row>
-    <row r="137" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D137" s="3"/>
     </row>
-    <row r="138" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D138" s="3"/>
     </row>
-    <row r="139" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D139" s="3"/>
     </row>
-    <row r="140" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D140" s="3"/>
     </row>
-    <row r="141" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D141" s="3"/>
     </row>
-    <row r="142" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D142" s="3"/>
     </row>
-    <row r="143" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D143" s="3"/>
     </row>
-    <row r="144" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D144" s="3"/>
     </row>
-    <row r="145" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D145" s="3"/>
     </row>
-    <row r="146" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D146" s="3"/>
     </row>
-    <row r="147" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D147" s="3"/>
     </row>
-    <row r="148" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D148" s="3"/>
     </row>
   </sheetData>
